--- a/output/Unassigned_Points_compact.xlsx
+++ b/output/Unassigned_Points_compact.xlsx
@@ -44363,7 +44363,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>N_1481</t>
+          <t>N_1480</t>
         </is>
       </c>
       <c r="B977" t="n">
@@ -44408,7 +44408,7 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>N_1484</t>
+          <t>N_1483</t>
         </is>
       </c>
       <c r="B978" t="n">
@@ -44453,7 +44453,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>N_1486</t>
+          <t>N_1485</t>
         </is>
       </c>
       <c r="B979" t="n">
@@ -44498,7 +44498,7 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>N_1487</t>
+          <t>N_1486</t>
         </is>
       </c>
       <c r="B980" t="n">
@@ -44543,7 +44543,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>N_1490</t>
+          <t>N_1489</t>
         </is>
       </c>
       <c r="B981" t="n">
@@ -44588,7 +44588,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>N_1491</t>
+          <t>N_1490</t>
         </is>
       </c>
       <c r="B982" t="n">
@@ -44633,7 +44633,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>N_1497</t>
+          <t>N_1494</t>
         </is>
       </c>
       <c r="B983" t="n">
@@ -44678,7 +44678,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>N_1503</t>
+          <t>N_1499</t>
         </is>
       </c>
       <c r="B984" t="n">
@@ -44723,7 +44723,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>N_1504</t>
+          <t>N_1500</t>
         </is>
       </c>
       <c r="B985" t="n">
@@ -44768,7 +44768,7 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>N_1505</t>
+          <t>N_1501</t>
         </is>
       </c>
       <c r="B986" t="n">
@@ -44813,7 +44813,7 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>N_1506</t>
+          <t>N_1502</t>
         </is>
       </c>
       <c r="B987" t="n">
@@ -44858,7 +44858,7 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>N_1508</t>
+          <t>N_1503</t>
         </is>
       </c>
       <c r="B988" t="n">
@@ -44903,7 +44903,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>N_1509</t>
+          <t>N_1504</t>
         </is>
       </c>
       <c r="B989" t="n">
@@ -44948,7 +44948,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>N_1510</t>
+          <t>N_1505</t>
         </is>
       </c>
       <c r="B990" t="n">
@@ -44993,7 +44993,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>N_1511</t>
+          <t>N_1506</t>
         </is>
       </c>
       <c r="B991" t="n">
@@ -45038,7 +45038,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>N_1512</t>
+          <t>N_1507</t>
         </is>
       </c>
       <c r="B992" t="n">
@@ -45083,7 +45083,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>N_1514</t>
+          <t>N_1509</t>
         </is>
       </c>
       <c r="B993" t="n">
@@ -45128,7 +45128,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>N_1516</t>
+          <t>N_1511</t>
         </is>
       </c>
       <c r="B994" t="n">
@@ -45173,7 +45173,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>N_1517</t>
+          <t>N_1512</t>
         </is>
       </c>
       <c r="B995" t="n">
@@ -45218,7 +45218,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>N_1519</t>
+          <t>N_1514</t>
         </is>
       </c>
       <c r="B996" t="n">
@@ -45263,7 +45263,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>N_1522</t>
+          <t>N_1516</t>
         </is>
       </c>
       <c r="B997" t="n">
@@ -45308,7 +45308,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>N_1523</t>
+          <t>N_1517</t>
         </is>
       </c>
       <c r="B998" t="n">
@@ -45353,7 +45353,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>N_1524</t>
+          <t>N_1518</t>
         </is>
       </c>
       <c r="B999" t="n">
@@ -45398,7 +45398,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>N_1530</t>
+          <t>N_1523</t>
         </is>
       </c>
       <c r="B1000" t="n">
@@ -45443,7 +45443,7 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>N_1531</t>
+          <t>N_1524</t>
         </is>
       </c>
       <c r="B1001" t="n">
@@ -45488,7 +45488,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>N_1533</t>
+          <t>N_1526</t>
         </is>
       </c>
       <c r="B1002" t="n">
@@ -45533,7 +45533,7 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>N_1534</t>
+          <t>N_1527</t>
         </is>
       </c>
       <c r="B1003" t="n">
@@ -45578,7 +45578,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>N_1537</t>
+          <t>N_1530</t>
         </is>
       </c>
       <c r="B1004" t="n">
@@ -45623,7 +45623,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>N_1538</t>
+          <t>N_1531</t>
         </is>
       </c>
       <c r="B1005" t="n">
@@ -45668,7 +45668,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>N_1540</t>
+          <t>N_1533</t>
         </is>
       </c>
       <c r="B1006" t="n">
@@ -45713,7 +45713,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>N_1543</t>
+          <t>N_1536</t>
         </is>
       </c>
       <c r="B1007" t="n">
@@ -45758,7 +45758,7 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>N_1544</t>
+          <t>N_1537</t>
         </is>
       </c>
       <c r="B1008" t="n">
@@ -45803,7 +45803,7 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>N_1545</t>
+          <t>N_1538</t>
         </is>
       </c>
       <c r="B1009" t="n">
@@ -45848,7 +45848,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>N_1546</t>
+          <t>N_1539</t>
         </is>
       </c>
       <c r="B1010" t="n">
@@ -45893,7 +45893,7 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>N_1548</t>
+          <t>N_1541</t>
         </is>
       </c>
       <c r="B1011" t="n">
@@ -45938,7 +45938,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>N_1549</t>
+          <t>N_1542</t>
         </is>
       </c>
       <c r="B1012" t="n">
@@ -45983,7 +45983,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>N_1550</t>
+          <t>N_1543</t>
         </is>
       </c>
       <c r="B1013" t="n">
@@ -46028,7 +46028,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>N_1552</t>
+          <t>N_1545</t>
         </is>
       </c>
       <c r="B1014" t="n">
@@ -46073,7 +46073,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>N_1553</t>
+          <t>N_1546</t>
         </is>
       </c>
       <c r="B1015" t="n">
@@ -46118,7 +46118,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>N_1554</t>
+          <t>N_1547</t>
         </is>
       </c>
       <c r="B1016" t="n">
@@ -46163,7 +46163,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>N_1555</t>
+          <t>N_1548</t>
         </is>
       </c>
       <c r="B1017" t="n">
@@ -46208,7 +46208,7 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>N_1556</t>
+          <t>N_1549</t>
         </is>
       </c>
       <c r="B1018" t="n">
@@ -46253,7 +46253,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>N_1557</t>
+          <t>N_1550</t>
         </is>
       </c>
       <c r="B1019" t="n">
@@ -46298,7 +46298,7 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>N_1558</t>
+          <t>N_1551</t>
         </is>
       </c>
       <c r="B1020" t="n">
@@ -46343,7 +46343,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>N_1559</t>
+          <t>N_1552</t>
         </is>
       </c>
       <c r="B1021" t="n">
@@ -46388,7 +46388,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>N_1561</t>
+          <t>N_1554</t>
         </is>
       </c>
       <c r="B1022" t="n">
@@ -46433,7 +46433,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>N_1562</t>
+          <t>N_1555</t>
         </is>
       </c>
       <c r="B1023" t="n">
@@ -46478,7 +46478,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>N_1563</t>
+          <t>N_1556</t>
         </is>
       </c>
       <c r="B1024" t="n">
@@ -46523,7 +46523,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>N_1564</t>
+          <t>N_1557</t>
         </is>
       </c>
       <c r="B1025" t="n">
@@ -46568,7 +46568,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>N_1565</t>
+          <t>N_1558</t>
         </is>
       </c>
       <c r="B1026" t="n">
@@ -46613,7 +46613,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>N_1567</t>
+          <t>N_1560</t>
         </is>
       </c>
       <c r="B1027" t="n">
@@ -46658,7 +46658,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>N_1570</t>
+          <t>N_1563</t>
         </is>
       </c>
       <c r="B1028" t="n">
@@ -46703,7 +46703,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>N_1572</t>
+          <t>N_1565</t>
         </is>
       </c>
       <c r="B1029" t="n">
@@ -46748,7 +46748,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>N_1573</t>
+          <t>N_1566</t>
         </is>
       </c>
       <c r="B1030" t="n">
@@ -46793,7 +46793,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>N_1575</t>
+          <t>N_1568</t>
         </is>
       </c>
       <c r="B1031" t="n">
@@ -46838,7 +46838,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>N_1576</t>
+          <t>N_1569</t>
         </is>
       </c>
       <c r="B1032" t="n">
@@ -46883,7 +46883,7 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>N_1577</t>
+          <t>N_1570</t>
         </is>
       </c>
       <c r="B1033" t="n">
@@ -46928,7 +46928,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>N_1578</t>
+          <t>N_1571</t>
         </is>
       </c>
       <c r="B1034" t="n">
@@ -46973,7 +46973,7 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>N_1579</t>
+          <t>N_1572</t>
         </is>
       </c>
       <c r="B1035" t="n">
@@ -47018,7 +47018,7 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>N_1580</t>
+          <t>N_1573</t>
         </is>
       </c>
       <c r="B1036" t="n">
@@ -47063,7 +47063,7 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>N_1581</t>
+          <t>N_1574</t>
         </is>
       </c>
       <c r="B1037" t="n">
@@ -47108,7 +47108,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>N_1582</t>
+          <t>N_1575</t>
         </is>
       </c>
       <c r="B1038" t="n">
@@ -47153,7 +47153,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>N_1583</t>
+          <t>N_1576</t>
         </is>
       </c>
       <c r="B1039" t="n">
@@ -47198,7 +47198,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>N_1584</t>
+          <t>N_1577</t>
         </is>
       </c>
       <c r="B1040" t="n">
@@ -47243,7 +47243,7 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>N_1585</t>
+          <t>N_1578</t>
         </is>
       </c>
       <c r="B1041" t="n">
@@ -47288,7 +47288,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>N_1586</t>
+          <t>N_1579</t>
         </is>
       </c>
       <c r="B1042" t="n">
@@ -47333,7 +47333,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>N_1587</t>
+          <t>N_1580</t>
         </is>
       </c>
       <c r="B1043" t="n">
@@ -47378,7 +47378,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>N_1588</t>
+          <t>N_1581</t>
         </is>
       </c>
       <c r="B1044" t="n">
@@ -47423,7 +47423,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>N_1589</t>
+          <t>N_1582</t>
         </is>
       </c>
       <c r="B1045" t="n">
@@ -47468,7 +47468,7 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>N_1590</t>
+          <t>N_1583</t>
         </is>
       </c>
       <c r="B1046" t="n">
@@ -47513,7 +47513,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>N_1591</t>
+          <t>N_1584</t>
         </is>
       </c>
       <c r="B1047" t="n">
@@ -47558,7 +47558,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>N_1593</t>
+          <t>N_1586</t>
         </is>
       </c>
       <c r="B1048" t="n">
@@ -47603,7 +47603,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>N_1594</t>
+          <t>N_1587</t>
         </is>
       </c>
       <c r="B1049" t="n">
@@ -47648,7 +47648,7 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>N_1596</t>
+          <t>N_1589</t>
         </is>
       </c>
       <c r="B1050" t="n">
@@ -47693,7 +47693,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>N_1597</t>
+          <t>N_1590</t>
         </is>
       </c>
       <c r="B1051" t="n">
@@ -47738,7 +47738,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>N_1599</t>
+          <t>N_1592</t>
         </is>
       </c>
       <c r="B1052" t="n">
@@ -47783,7 +47783,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>N_1600</t>
+          <t>N_1593</t>
         </is>
       </c>
       <c r="B1053" t="n">
@@ -47828,7 +47828,7 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>N_1605</t>
+          <t>N_1598</t>
         </is>
       </c>
       <c r="B1054" t="n">
@@ -47873,7 +47873,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>N_1606</t>
+          <t>N_1599</t>
         </is>
       </c>
       <c r="B1055" t="n">
@@ -47918,7 +47918,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>N_1607</t>
+          <t>N_1600</t>
         </is>
       </c>
       <c r="B1056" t="n">
@@ -47963,7 +47963,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>N_1608</t>
+          <t>N_1601</t>
         </is>
       </c>
       <c r="B1057" t="n">
@@ -48008,7 +48008,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>N_1609</t>
+          <t>N_1602</t>
         </is>
       </c>
       <c r="B1058" t="n">
@@ -48053,7 +48053,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>N_1611</t>
+          <t>N_1604</t>
         </is>
       </c>
       <c r="B1059" t="n">
@@ -48098,7 +48098,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>N_1612</t>
+          <t>N_1605</t>
         </is>
       </c>
       <c r="B1060" t="n">
@@ -48143,7 +48143,7 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>N_1614</t>
+          <t>N_1607</t>
         </is>
       </c>
       <c r="B1061" t="n">
@@ -48188,7 +48188,7 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>N_1615</t>
+          <t>N_1608</t>
         </is>
       </c>
       <c r="B1062" t="n">
@@ -48233,7 +48233,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>N_1616</t>
+          <t>N_1609</t>
         </is>
       </c>
       <c r="B1063" t="n">
@@ -48278,7 +48278,7 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>N_1617</t>
+          <t>N_1610</t>
         </is>
       </c>
       <c r="B1064" t="n">
@@ -48323,7 +48323,7 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>N_1618</t>
+          <t>N_1611</t>
         </is>
       </c>
       <c r="B1065" t="n">
@@ -48368,7 +48368,7 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>N_1619</t>
+          <t>N_1612</t>
         </is>
       </c>
       <c r="B1066" t="n">
@@ -48413,7 +48413,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>N_1620</t>
+          <t>N_1613</t>
         </is>
       </c>
       <c r="B1067" t="n">
@@ -48458,7 +48458,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>N_1621</t>
+          <t>N_1614</t>
         </is>
       </c>
       <c r="B1068" t="n">
@@ -48503,7 +48503,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>N_1622</t>
+          <t>N_1615</t>
         </is>
       </c>
       <c r="B1069" t="n">
@@ -48548,7 +48548,7 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>N_1623</t>
+          <t>N_1616</t>
         </is>
       </c>
       <c r="B1070" t="n">
@@ -48593,7 +48593,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>N_1625</t>
+          <t>N_1618</t>
         </is>
       </c>
       <c r="B1071" t="n">
@@ -48638,7 +48638,7 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>N_1627</t>
+          <t>N_1620</t>
         </is>
       </c>
       <c r="B1072" t="n">
@@ -48683,7 +48683,7 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>N_1628</t>
+          <t>N_1621</t>
         </is>
       </c>
       <c r="B1073" t="n">
@@ -48728,7 +48728,7 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>N_1630</t>
+          <t>N_1623</t>
         </is>
       </c>
       <c r="B1074" t="n">
@@ -48773,7 +48773,7 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>N_1631</t>
+          <t>N_1624</t>
         </is>
       </c>
       <c r="B1075" t="n">
@@ -48818,7 +48818,7 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>N_1632</t>
+          <t>N_1625</t>
         </is>
       </c>
       <c r="B1076" t="n">
@@ -48863,7 +48863,7 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>N_1633</t>
+          <t>N_1626</t>
         </is>
       </c>
       <c r="B1077" t="n">
@@ -48908,7 +48908,7 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>N_1634</t>
+          <t>N_1627</t>
         </is>
       </c>
       <c r="B1078" t="n">
@@ -48953,7 +48953,7 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>N_1636</t>
+          <t>N_1629</t>
         </is>
       </c>
       <c r="B1079" t="n">
@@ -48998,7 +48998,7 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>N_1638</t>
+          <t>N_1631</t>
         </is>
       </c>
       <c r="B1080" t="n">
@@ -49043,7 +49043,7 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>N_1639</t>
+          <t>N_1632</t>
         </is>
       </c>
       <c r="B1081" t="n">
@@ -49088,7 +49088,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>N_1640</t>
+          <t>N_1633</t>
         </is>
       </c>
       <c r="B1082" t="n">
@@ -49133,7 +49133,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>N_1641</t>
+          <t>N_1634</t>
         </is>
       </c>
       <c r="B1083" t="n">
@@ -49178,7 +49178,7 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>N_1642</t>
+          <t>N_1635</t>
         </is>
       </c>
       <c r="B1084" t="n">
@@ -49223,7 +49223,7 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>N_1643</t>
+          <t>N_1636</t>
         </is>
       </c>
       <c r="B1085" t="n">
@@ -49268,7 +49268,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>N_1644</t>
+          <t>N_1637</t>
         </is>
       </c>
       <c r="B1086" t="n">
@@ -49313,7 +49313,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>N_1645</t>
+          <t>N_1638</t>
         </is>
       </c>
       <c r="B1087" t="n">
@@ -49358,7 +49358,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>N_1646</t>
+          <t>N_1639</t>
         </is>
       </c>
       <c r="B1088" t="n">
@@ -49403,7 +49403,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>N_1647</t>
+          <t>N_1640</t>
         </is>
       </c>
       <c r="B1089" t="n">
@@ -49448,7 +49448,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>N_1649</t>
+          <t>N_1642</t>
         </is>
       </c>
       <c r="B1090" t="n">
@@ -49493,7 +49493,7 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>N_1650</t>
+          <t>N_1643</t>
         </is>
       </c>
       <c r="B1091" t="n">
@@ -49538,7 +49538,7 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>N_1651</t>
+          <t>N_1644</t>
         </is>
       </c>
       <c r="B1092" t="n">
@@ -49583,7 +49583,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>N_1652</t>
+          <t>N_1645</t>
         </is>
       </c>
       <c r="B1093" t="n">
@@ -49628,7 +49628,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>N_1653</t>
+          <t>N_1646</t>
         </is>
       </c>
       <c r="B1094" t="n">
@@ -49673,7 +49673,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>N_1654</t>
+          <t>N_1647</t>
         </is>
       </c>
       <c r="B1095" t="n">
@@ -49718,7 +49718,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>N_1655</t>
+          <t>N_1648</t>
         </is>
       </c>
       <c r="B1096" t="n">
@@ -49763,7 +49763,7 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>N_1656</t>
+          <t>N_1649</t>
         </is>
       </c>
       <c r="B1097" t="n">
@@ -49808,7 +49808,7 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>N_1657</t>
+          <t>N_1650</t>
         </is>
       </c>
       <c r="B1098" t="n">
@@ -49853,7 +49853,7 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>N_1660</t>
+          <t>N_1653</t>
         </is>
       </c>
       <c r="B1099" t="n">
@@ -49898,7 +49898,7 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>N_1661</t>
+          <t>N_1654</t>
         </is>
       </c>
       <c r="B1100" t="n">
@@ -49943,7 +49943,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>N_1662</t>
+          <t>N_1655</t>
         </is>
       </c>
       <c r="B1101" t="n">
@@ -49988,7 +49988,7 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>N_1663</t>
+          <t>N_1656</t>
         </is>
       </c>
       <c r="B1102" t="n">
@@ -50033,7 +50033,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>N_1668</t>
+          <t>N_1661</t>
         </is>
       </c>
       <c r="B1103" t="n">
@@ -50078,7 +50078,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>N_1670</t>
+          <t>N_1663</t>
         </is>
       </c>
       <c r="B1104" t="n">
@@ -50123,7 +50123,7 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>N_1671</t>
+          <t>N_1664</t>
         </is>
       </c>
       <c r="B1105" t="n">
@@ -50168,7 +50168,7 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>N_1672</t>
+          <t>N_1665</t>
         </is>
       </c>
       <c r="B1106" t="n">
@@ -50213,7 +50213,7 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>N_1673</t>
+          <t>N_1666</t>
         </is>
       </c>
       <c r="B1107" t="n">
@@ -50258,7 +50258,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>N_1675</t>
+          <t>N_1668</t>
         </is>
       </c>
       <c r="B1108" t="n">
@@ -50303,7 +50303,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>N_1677</t>
+          <t>N_1670</t>
         </is>
       </c>
       <c r="B1109" t="n">
@@ -50348,7 +50348,7 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>N_1679</t>
+          <t>N_1672</t>
         </is>
       </c>
       <c r="B1110" t="n">
@@ -50393,7 +50393,7 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>N_1681</t>
+          <t>N_1674</t>
         </is>
       </c>
       <c r="B1111" t="n">
@@ -50438,7 +50438,7 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>N_1682</t>
+          <t>N_1675</t>
         </is>
       </c>
       <c r="B1112" t="n">
@@ -50483,7 +50483,7 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>N_1683</t>
+          <t>N_1676</t>
         </is>
       </c>
       <c r="B1113" t="n">
@@ -50528,7 +50528,7 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>N_1685</t>
+          <t>N_1678</t>
         </is>
       </c>
       <c r="B1114" t="n">
@@ -50573,7 +50573,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>N_1686</t>
+          <t>N_1679</t>
         </is>
       </c>
       <c r="B1115" t="n">
@@ -50618,7 +50618,7 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>N_1687</t>
+          <t>N_1680</t>
         </is>
       </c>
       <c r="B1116" t="n">
@@ -50663,7 +50663,7 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>N_1688</t>
+          <t>N_1681</t>
         </is>
       </c>
       <c r="B1117" t="n">
@@ -50708,7 +50708,7 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>N_1689</t>
+          <t>N_1682</t>
         </is>
       </c>
       <c r="B1118" t="n">
@@ -50753,7 +50753,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>N_1690</t>
+          <t>N_1683</t>
         </is>
       </c>
       <c r="B1119" t="n">
@@ -50798,7 +50798,7 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>N_1691</t>
+          <t>N_1684</t>
         </is>
       </c>
       <c r="B1120" t="n">
@@ -50843,7 +50843,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>N_1693</t>
+          <t>N_1686</t>
         </is>
       </c>
       <c r="B1121" t="n">
@@ -50888,7 +50888,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>N_1694</t>
+          <t>N_1687</t>
         </is>
       </c>
       <c r="B1122" t="n">
@@ -50933,7 +50933,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>N_1698</t>
+          <t>N_1691</t>
         </is>
       </c>
       <c r="B1123" t="n">
@@ -50978,7 +50978,7 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>N_1699</t>
+          <t>N_1692</t>
         </is>
       </c>
       <c r="B1124" t="n">
@@ -51023,7 +51023,7 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>N_1701</t>
+          <t>N_1694</t>
         </is>
       </c>
       <c r="B1125" t="n">
@@ -51068,7 +51068,7 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>N_1704</t>
+          <t>N_1697</t>
         </is>
       </c>
       <c r="B1126" t="n">
@@ -51113,7 +51113,7 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>N_1705</t>
+          <t>N_1698</t>
         </is>
       </c>
       <c r="B1127" t="n">
@@ -51158,7 +51158,7 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>N_1706</t>
+          <t>N_1699</t>
         </is>
       </c>
       <c r="B1128" t="n">
@@ -51203,7 +51203,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>N_1707</t>
+          <t>N_1700</t>
         </is>
       </c>
       <c r="B1129" t="n">
@@ -51248,7 +51248,7 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>N_1708</t>
+          <t>N_1701</t>
         </is>
       </c>
       <c r="B1130" t="n">
@@ -51293,7 +51293,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>N_1709</t>
+          <t>N_1702</t>
         </is>
       </c>
       <c r="B1131" t="n">
@@ -51338,7 +51338,7 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>N_1712</t>
+          <t>N_1705</t>
         </is>
       </c>
       <c r="B1132" t="n">
@@ -51383,7 +51383,7 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>N_1717</t>
+          <t>N_1710</t>
         </is>
       </c>
       <c r="B1133" t="n">
@@ -51428,7 +51428,7 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>N_1718</t>
+          <t>N_1711</t>
         </is>
       </c>
       <c r="B1134" t="n">
@@ -51473,7 +51473,7 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>N_1719</t>
+          <t>N_1712</t>
         </is>
       </c>
       <c r="B1135" t="n">
@@ -51518,7 +51518,7 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>N_1721</t>
+          <t>N_1714</t>
         </is>
       </c>
       <c r="B1136" t="n">
@@ -51563,7 +51563,7 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>N_1722</t>
+          <t>N_1715</t>
         </is>
       </c>
       <c r="B1137" t="n">
@@ -51608,7 +51608,7 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>N_1723</t>
+          <t>N_1716</t>
         </is>
       </c>
       <c r="B1138" t="n">
@@ -51653,7 +51653,7 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>N_1724</t>
+          <t>N_1717</t>
         </is>
       </c>
       <c r="B1139" t="n">
@@ -51698,7 +51698,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>N_1725</t>
+          <t>N_1718</t>
         </is>
       </c>
       <c r="B1140" t="n">
@@ -51743,7 +51743,7 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>N_1726</t>
+          <t>N_1719</t>
         </is>
       </c>
       <c r="B1141" t="n">
@@ -51788,7 +51788,7 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>N_1729</t>
+          <t>N_1722</t>
         </is>
       </c>
       <c r="B1142" t="n">
@@ -51833,7 +51833,7 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>N_1730</t>
+          <t>N_1723</t>
         </is>
       </c>
       <c r="B1143" t="n">
@@ -51878,7 +51878,7 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>N_1734</t>
+          <t>N_1727</t>
         </is>
       </c>
       <c r="B1144" t="n">
@@ -51923,7 +51923,7 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>N_1738</t>
+          <t>N_1731</t>
         </is>
       </c>
       <c r="B1145" t="n">
@@ -51968,7 +51968,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>N_1741</t>
+          <t>N_1734</t>
         </is>
       </c>
       <c r="B1146" t="n">
@@ -52013,7 +52013,7 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>N_1743</t>
+          <t>N_1736</t>
         </is>
       </c>
       <c r="B1147" t="n">
@@ -52058,7 +52058,7 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>N_1744</t>
+          <t>N_1737</t>
         </is>
       </c>
       <c r="B1148" t="n">
@@ -52103,7 +52103,7 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>N_1747</t>
+          <t>N_1740</t>
         </is>
       </c>
       <c r="B1149" t="n">
@@ -52148,7 +52148,7 @@
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>N_1748</t>
+          <t>N_1741</t>
         </is>
       </c>
       <c r="B1150" t="n">
@@ -52193,7 +52193,7 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>N_1750</t>
+          <t>N_1743</t>
         </is>
       </c>
       <c r="B1151" t="n">
@@ -52238,7 +52238,7 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>N_1752</t>
+          <t>N_1745</t>
         </is>
       </c>
       <c r="B1152" t="n">
@@ -52283,7 +52283,7 @@
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>N_1753</t>
+          <t>N_1746</t>
         </is>
       </c>
       <c r="B1153" t="n">
@@ -52328,7 +52328,7 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>N_1754</t>
+          <t>N_1747</t>
         </is>
       </c>
       <c r="B1154" t="n">
@@ -52373,7 +52373,7 @@
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>N_1755</t>
+          <t>N_1748</t>
         </is>
       </c>
       <c r="B1155" t="n">
@@ -52418,7 +52418,7 @@
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>N_1756</t>
+          <t>N_1749</t>
         </is>
       </c>
       <c r="B1156" t="n">
@@ -52463,7 +52463,7 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>N_1757</t>
+          <t>N_1750</t>
         </is>
       </c>
       <c r="B1157" t="n">
@@ -52508,7 +52508,7 @@
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>N_1758</t>
+          <t>N_1751</t>
         </is>
       </c>
       <c r="B1158" t="n">
@@ -52553,7 +52553,7 @@
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>N_1760</t>
+          <t>N_1753</t>
         </is>
       </c>
       <c r="B1159" t="n">
@@ -52598,7 +52598,7 @@
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>N_1761</t>
+          <t>N_1754</t>
         </is>
       </c>
       <c r="B1160" t="n">
@@ -52643,7 +52643,7 @@
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>N_1762</t>
+          <t>N_1755</t>
         </is>
       </c>
       <c r="B1161" t="n">
@@ -52688,7 +52688,7 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>N_1763</t>
+          <t>N_1756</t>
         </is>
       </c>
       <c r="B1162" t="n">
@@ -52733,7 +52733,7 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>N_1765</t>
+          <t>N_1758</t>
         </is>
       </c>
       <c r="B1163" t="n">
@@ -52778,7 +52778,7 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>N_1767</t>
+          <t>N_1760</t>
         </is>
       </c>
       <c r="B1164" t="n">
@@ -52823,7 +52823,7 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>N_1768</t>
+          <t>N_1761</t>
         </is>
       </c>
       <c r="B1165" t="n">
@@ -52868,7 +52868,7 @@
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>N_1769</t>
+          <t>N_1762</t>
         </is>
       </c>
       <c r="B1166" t="n">
@@ -52913,7 +52913,7 @@
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>N_1771</t>
+          <t>N_1764</t>
         </is>
       </c>
       <c r="B1167" t="n">
@@ -52958,7 +52958,7 @@
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>N_1774</t>
+          <t>N_1767</t>
         </is>
       </c>
       <c r="B1168" t="n">
@@ -53003,7 +53003,7 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>N_1775</t>
+          <t>N_1768</t>
         </is>
       </c>
       <c r="B1169" t="n">
@@ -53048,7 +53048,7 @@
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>N_1776</t>
+          <t>N_1769</t>
         </is>
       </c>
       <c r="B1170" t="n">
@@ -53093,7 +53093,7 @@
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>N_1777</t>
+          <t>N_1770</t>
         </is>
       </c>
       <c r="B1171" t="n">
@@ -53138,7 +53138,7 @@
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>N_1778</t>
+          <t>N_1771</t>
         </is>
       </c>
       <c r="B1172" t="n">
@@ -53183,7 +53183,7 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>N_1779</t>
+          <t>N_1772</t>
         </is>
       </c>
       <c r="B1173" t="n">
@@ -53228,7 +53228,7 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>N_1780</t>
+          <t>N_1773</t>
         </is>
       </c>
       <c r="B1174" t="n">
@@ -53273,7 +53273,7 @@
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>N_1781</t>
+          <t>N_1774</t>
         </is>
       </c>
       <c r="B1175" t="n">
@@ -53318,7 +53318,7 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>N_1782</t>
+          <t>N_1775</t>
         </is>
       </c>
       <c r="B1176" t="n">
@@ -53363,7 +53363,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>N_1784</t>
+          <t>N_1777</t>
         </is>
       </c>
       <c r="B1177" t="n">
@@ -53408,7 +53408,7 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>N_1785</t>
+          <t>N_1778</t>
         </is>
       </c>
       <c r="B1178" t="n">
@@ -53453,7 +53453,7 @@
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>N_1786</t>
+          <t>N_1779</t>
         </is>
       </c>
       <c r="B1179" t="n">
@@ -53498,7 +53498,7 @@
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>N_1790</t>
+          <t>N_1783</t>
         </is>
       </c>
       <c r="B1180" t="n">
@@ -53543,7 +53543,7 @@
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>N_1792</t>
+          <t>N_1785</t>
         </is>
       </c>
       <c r="B1181" t="n">
@@ -53588,7 +53588,7 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>N_1796</t>
+          <t>N_1789</t>
         </is>
       </c>
       <c r="B1182" t="n">
@@ -53633,7 +53633,7 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>N_1798</t>
+          <t>N_1791</t>
         </is>
       </c>
       <c r="B1183" t="n">
@@ -53678,7 +53678,7 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>N_1799</t>
+          <t>N_1792</t>
         </is>
       </c>
       <c r="B1184" t="n">
@@ -53723,7 +53723,7 @@
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>N_1800</t>
+          <t>N_1793</t>
         </is>
       </c>
       <c r="B1185" t="n">
@@ -53768,7 +53768,7 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>N_1801</t>
+          <t>N_1794</t>
         </is>
       </c>
       <c r="B1186" t="n">
@@ -53813,7 +53813,7 @@
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>N_1802</t>
+          <t>N_1795</t>
         </is>
       </c>
       <c r="B1187" t="n">
@@ -53858,7 +53858,7 @@
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>N_1803</t>
+          <t>N_1796</t>
         </is>
       </c>
       <c r="B1188" t="n">
@@ -53903,7 +53903,7 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>N_1804</t>
+          <t>N_1797</t>
         </is>
       </c>
       <c r="B1189" t="n">
@@ -53948,7 +53948,7 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>N_1808</t>
+          <t>N_1801</t>
         </is>
       </c>
       <c r="B1190" t="n">
@@ -53993,7 +53993,7 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>N_1809</t>
+          <t>N_1802</t>
         </is>
       </c>
       <c r="B1191" t="n">
@@ -54038,7 +54038,7 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>N_1810</t>
+          <t>N_1803</t>
         </is>
       </c>
       <c r="B1192" t="n">
@@ -54083,7 +54083,7 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>N_1811</t>
+          <t>N_1804</t>
         </is>
       </c>
       <c r="B1193" t="n">
@@ -54128,7 +54128,7 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>N_1812</t>
+          <t>N_1805</t>
         </is>
       </c>
       <c r="B1194" t="n">
@@ -54173,7 +54173,7 @@
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>N_1813</t>
+          <t>N_1806</t>
         </is>
       </c>
       <c r="B1195" t="n">
@@ -54218,7 +54218,7 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>N_1814</t>
+          <t>N_1807</t>
         </is>
       </c>
       <c r="B1196" t="n">
@@ -54263,7 +54263,7 @@
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>N_1816</t>
+          <t>N_1809</t>
         </is>
       </c>
       <c r="B1197" t="n">
@@ -54308,7 +54308,7 @@
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>N_1817</t>
+          <t>N_1810</t>
         </is>
       </c>
       <c r="B1198" t="n">
@@ -54353,7 +54353,7 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>N_1819</t>
+          <t>N_1812</t>
         </is>
       </c>
       <c r="B1199" t="n">
@@ -54398,7 +54398,7 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>N_1820</t>
+          <t>N_1813</t>
         </is>
       </c>
       <c r="B1200" t="n">
@@ -54443,7 +54443,7 @@
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>N_1821</t>
+          <t>N_1814</t>
         </is>
       </c>
       <c r="B1201" t="n">
@@ -54488,7 +54488,7 @@
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>N_1822</t>
+          <t>N_1815</t>
         </is>
       </c>
       <c r="B1202" t="n">
@@ -54533,7 +54533,7 @@
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>N_1826</t>
+          <t>N_1819</t>
         </is>
       </c>
       <c r="B1203" t="n">
@@ -54578,7 +54578,7 @@
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>N_1829</t>
+          <t>N_1822</t>
         </is>
       </c>
       <c r="B1204" t="n">
@@ -54623,7 +54623,7 @@
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>N_1830</t>
+          <t>N_1823</t>
         </is>
       </c>
       <c r="B1205" t="n">
@@ -54668,7 +54668,7 @@
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>N_1831</t>
+          <t>N_1824</t>
         </is>
       </c>
       <c r="B1206" t="n">
@@ -54713,7 +54713,7 @@
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>N_1833</t>
+          <t>N_1826</t>
         </is>
       </c>
       <c r="B1207" t="n">
@@ -54758,7 +54758,7 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>N_1838</t>
+          <t>N_1831</t>
         </is>
       </c>
       <c r="B1208" t="n">
@@ -54803,7 +54803,7 @@
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>N_1841</t>
+          <t>N_1834</t>
         </is>
       </c>
       <c r="B1209" t="n">
@@ -54848,7 +54848,7 @@
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>N_1842</t>
+          <t>N_1835</t>
         </is>
       </c>
       <c r="B1210" t="n">
@@ -54893,7 +54893,7 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>N_1843</t>
+          <t>N_1836</t>
         </is>
       </c>
       <c r="B1211" t="n">
@@ -54938,7 +54938,7 @@
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>N_1844</t>
+          <t>N_1837</t>
         </is>
       </c>
       <c r="B1212" t="n">
@@ -54983,7 +54983,7 @@
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>N_1845</t>
+          <t>N_1838</t>
         </is>
       </c>
       <c r="B1213" t="n">
@@ -55028,7 +55028,7 @@
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>N_1846</t>
+          <t>N_1839</t>
         </is>
       </c>
       <c r="B1214" t="n">
@@ -55073,7 +55073,7 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>N_1850</t>
+          <t>N_1843</t>
         </is>
       </c>
       <c r="B1215" t="n">
@@ -55118,7 +55118,7 @@
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>N_1851</t>
+          <t>N_1844</t>
         </is>
       </c>
       <c r="B1216" t="n">
@@ -55163,7 +55163,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>N_1855</t>
+          <t>N_1848</t>
         </is>
       </c>
       <c r="B1217" t="n">
@@ -55208,7 +55208,7 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>N_1856</t>
+          <t>N_1849</t>
         </is>
       </c>
       <c r="B1218" t="n">
@@ -55253,7 +55253,7 @@
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>N_1857</t>
+          <t>N_1850</t>
         </is>
       </c>
       <c r="B1219" t="n">
@@ -55298,7 +55298,7 @@
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>N_1862</t>
+          <t>N_1855</t>
         </is>
       </c>
       <c r="B1220" t="n">
@@ -55343,7 +55343,7 @@
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>N_1865</t>
+          <t>N_1858</t>
         </is>
       </c>
       <c r="B1221" t="n">
@@ -55388,7 +55388,7 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>N_1866</t>
+          <t>N_1859</t>
         </is>
       </c>
       <c r="B1222" t="n">
@@ -55433,7 +55433,7 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>N_1869</t>
+          <t>N_1862</t>
         </is>
       </c>
       <c r="B1223" t="n">
@@ -55478,7 +55478,7 @@
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>N_1870</t>
+          <t>N_1863</t>
         </is>
       </c>
       <c r="B1224" t="n">
@@ -55523,7 +55523,7 @@
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>N_1871</t>
+          <t>N_1864</t>
         </is>
       </c>
       <c r="B1225" t="n">
@@ -55568,7 +55568,7 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>N_1876</t>
+          <t>N_1869</t>
         </is>
       </c>
       <c r="B1226" t="n">
@@ -55613,7 +55613,7 @@
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>N_1877</t>
+          <t>N_1870</t>
         </is>
       </c>
       <c r="B1227" t="n">
@@ -55658,7 +55658,7 @@
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>N_1878</t>
+          <t>N_1871</t>
         </is>
       </c>
       <c r="B1228" t="n">
@@ -55703,7 +55703,7 @@
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>N_1879</t>
+          <t>N_1872</t>
         </is>
       </c>
       <c r="B1229" t="n">
@@ -55748,7 +55748,7 @@
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>N_1880</t>
+          <t>N_1873</t>
         </is>
       </c>
       <c r="B1230" t="n">
@@ -55793,7 +55793,7 @@
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>N_1882</t>
+          <t>N_1875</t>
         </is>
       </c>
       <c r="B1231" t="n">
@@ -55838,7 +55838,7 @@
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>N_1883</t>
+          <t>N_1876</t>
         </is>
       </c>
       <c r="B1232" t="n">
@@ -55883,7 +55883,7 @@
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>N_1884</t>
+          <t>N_1877</t>
         </is>
       </c>
       <c r="B1233" t="n">
@@ -55928,7 +55928,7 @@
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>N_1886</t>
+          <t>N_1879</t>
         </is>
       </c>
       <c r="B1234" t="n">
@@ -55973,7 +55973,7 @@
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>N_1888</t>
+          <t>N_1881</t>
         </is>
       </c>
       <c r="B1235" t="n">
@@ -56018,7 +56018,7 @@
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>N_1889</t>
+          <t>N_1882</t>
         </is>
       </c>
       <c r="B1236" t="n">
@@ -56063,7 +56063,7 @@
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>N_1891</t>
+          <t>N_1884</t>
         </is>
       </c>
       <c r="B1237" t="n">
@@ -56108,7 +56108,7 @@
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>N_1895</t>
+          <t>N_1888</t>
         </is>
       </c>
       <c r="B1238" t="n">
@@ -56153,7 +56153,7 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>N_1897</t>
+          <t>N_1890</t>
         </is>
       </c>
       <c r="B1239" t="n">
@@ -56198,7 +56198,7 @@
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>N_1899</t>
+          <t>N_1892</t>
         </is>
       </c>
       <c r="B1240" t="n">
@@ -56243,7 +56243,7 @@
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>N_1903</t>
+          <t>N_1896</t>
         </is>
       </c>
       <c r="B1241" t="n">
@@ -56288,7 +56288,7 @@
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>N_1904</t>
+          <t>N_1897</t>
         </is>
       </c>
       <c r="B1242" t="n">
@@ -56333,7 +56333,7 @@
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>N_1905</t>
+          <t>N_1898</t>
         </is>
       </c>
       <c r="B1243" t="n">
@@ -56378,7 +56378,7 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>N_1910</t>
+          <t>N_1903</t>
         </is>
       </c>
       <c r="B1244" t="n">
@@ -56423,7 +56423,7 @@
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>N_1911</t>
+          <t>N_1904</t>
         </is>
       </c>
       <c r="B1245" t="n">
@@ -56468,7 +56468,7 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>N_1912</t>
+          <t>N_1905</t>
         </is>
       </c>
       <c r="B1246" t="n">
@@ -56513,7 +56513,7 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>N_1913</t>
+          <t>N_1906</t>
         </is>
       </c>
       <c r="B1247" t="n">
@@ -56558,7 +56558,7 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>N_1915</t>
+          <t>N_1908</t>
         </is>
       </c>
       <c r="B1248" t="n">
@@ -56603,7 +56603,7 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>N_1916</t>
+          <t>N_1909</t>
         </is>
       </c>
       <c r="B1249" t="n">
@@ -56648,7 +56648,7 @@
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>N_1919</t>
+          <t>N_1912</t>
         </is>
       </c>
       <c r="B1250" t="n">
@@ -56693,7 +56693,7 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>N_1923</t>
+          <t>N_1916</t>
         </is>
       </c>
       <c r="B1251" t="n">
@@ -56738,7 +56738,7 @@
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>N_1924</t>
+          <t>N_1917</t>
         </is>
       </c>
       <c r="B1252" t="n">
@@ -56783,7 +56783,7 @@
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>N_1928</t>
+          <t>N_1921</t>
         </is>
       </c>
       <c r="B1253" t="n">
@@ -56828,7 +56828,7 @@
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>N_1931</t>
+          <t>N_1924</t>
         </is>
       </c>
       <c r="B1254" t="n">
@@ -56873,7 +56873,7 @@
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>N_1932</t>
+          <t>N_1925</t>
         </is>
       </c>
       <c r="B1255" t="n">
@@ -56918,7 +56918,7 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>N_1937</t>
+          <t>N_1930</t>
         </is>
       </c>
       <c r="B1256" t="n">
@@ -56963,7 +56963,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>N_1940</t>
+          <t>N_1933</t>
         </is>
       </c>
       <c r="B1257" t="n">
@@ -57008,7 +57008,7 @@
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>N_1941</t>
+          <t>N_1934</t>
         </is>
       </c>
       <c r="B1258" t="n">
@@ -57053,7 +57053,7 @@
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>N_1942</t>
+          <t>N_1935</t>
         </is>
       </c>
       <c r="B1259" t="n">
@@ -57098,7 +57098,7 @@
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>N_1944</t>
+          <t>N_1937</t>
         </is>
       </c>
       <c r="B1260" t="n">
@@ -57143,7 +57143,7 @@
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>N_1946</t>
+          <t>N_1939</t>
         </is>
       </c>
       <c r="B1261" t="n">
@@ -57188,7 +57188,7 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>N_1947</t>
+          <t>N_1940</t>
         </is>
       </c>
       <c r="B1262" t="n">
@@ -57233,7 +57233,7 @@
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>N_1949</t>
+          <t>N_1942</t>
         </is>
       </c>
       <c r="B1263" t="n">
@@ -57278,7 +57278,7 @@
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>N_1951</t>
+          <t>N_1944</t>
         </is>
       </c>
       <c r="B1264" t="n">
@@ -57323,7 +57323,7 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>N_1952</t>
+          <t>N_1945</t>
         </is>
       </c>
       <c r="B1265" t="n">
@@ -57368,7 +57368,7 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>N_1957</t>
+          <t>N_1950</t>
         </is>
       </c>
       <c r="B1266" t="n">
@@ -57413,7 +57413,7 @@
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>N_1959</t>
+          <t>N_1952</t>
         </is>
       </c>
       <c r="B1267" t="n">
@@ -57458,7 +57458,7 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>N_1963</t>
+          <t>N_1956</t>
         </is>
       </c>
       <c r="B1268" t="n">
@@ -57503,7 +57503,7 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>N_1966</t>
+          <t>N_1959</t>
         </is>
       </c>
       <c r="B1269" t="n">
@@ -57548,7 +57548,7 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>N_1967</t>
+          <t>N_1960</t>
         </is>
       </c>
       <c r="B1270" t="n">
@@ -57593,7 +57593,7 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>N_1968</t>
+          <t>N_1961</t>
         </is>
       </c>
       <c r="B1271" t="n">
@@ -57638,7 +57638,7 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>N_1969</t>
+          <t>N_1962</t>
         </is>
       </c>
       <c r="B1272" t="n">
@@ -57683,7 +57683,7 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>N_1970</t>
+          <t>N_1963</t>
         </is>
       </c>
       <c r="B1273" t="n">
@@ -57728,7 +57728,7 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>N_1971</t>
+          <t>N_1964</t>
         </is>
       </c>
       <c r="B1274" t="n">
@@ -57773,7 +57773,7 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>N_1974</t>
+          <t>N_1967</t>
         </is>
       </c>
       <c r="B1275" t="n">
@@ -57818,7 +57818,7 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>N_1975</t>
+          <t>N_1968</t>
         </is>
       </c>
       <c r="B1276" t="n">
@@ -57863,7 +57863,7 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>N_1977</t>
+          <t>N_1970</t>
         </is>
       </c>
       <c r="B1277" t="n">
@@ -57908,7 +57908,7 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>N_1978</t>
+          <t>N_1971</t>
         </is>
       </c>
       <c r="B1278" t="n">
@@ -57953,7 +57953,7 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>N_1979</t>
+          <t>N_1972</t>
         </is>
       </c>
       <c r="B1279" t="n">
@@ -57998,7 +57998,7 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>N_1980</t>
+          <t>N_1973</t>
         </is>
       </c>
       <c r="B1280" t="n">
@@ -58043,7 +58043,7 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>N_1981</t>
+          <t>N_1974</t>
         </is>
       </c>
       <c r="B1281" t="n">
@@ -58088,7 +58088,7 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>N_1985</t>
+          <t>N_1978</t>
         </is>
       </c>
       <c r="B1282" t="n">
@@ -58133,7 +58133,7 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>N_1986</t>
+          <t>N_1979</t>
         </is>
       </c>
       <c r="B1283" t="n">
@@ -58178,7 +58178,7 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>N_1987</t>
+          <t>N_1980</t>
         </is>
       </c>
       <c r="B1284" t="n">
@@ -58223,7 +58223,7 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>N_1988</t>
+          <t>N_1981</t>
         </is>
       </c>
       <c r="B1285" t="n">
@@ -58268,7 +58268,7 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>N_1989</t>
+          <t>N_1982</t>
         </is>
       </c>
       <c r="B1286" t="n">
@@ -58313,7 +58313,7 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>N_1990</t>
+          <t>N_1983</t>
         </is>
       </c>
       <c r="B1287" t="n">
@@ -58358,7 +58358,7 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>N_1991</t>
+          <t>N_1984</t>
         </is>
       </c>
       <c r="B1288" t="n">
@@ -58403,7 +58403,7 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>N_1992</t>
+          <t>N_1985</t>
         </is>
       </c>
       <c r="B1289" t="n">
@@ -58448,7 +58448,7 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>N_1993</t>
+          <t>N_1986</t>
         </is>
       </c>
       <c r="B1290" t="n">
@@ -58493,7 +58493,7 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>N_1994</t>
+          <t>N_1987</t>
         </is>
       </c>
       <c r="B1291" t="n">
@@ -58538,7 +58538,7 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>N_1995</t>
+          <t>N_1988</t>
         </is>
       </c>
       <c r="B1292" t="n">
@@ -58583,7 +58583,7 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>N_1996</t>
+          <t>N_1989</t>
         </is>
       </c>
       <c r="B1293" t="n">
@@ -58628,7 +58628,7 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>N_1998</t>
+          <t>N_1991</t>
         </is>
       </c>
       <c r="B1294" t="n">
@@ -58673,7 +58673,7 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>N_1999</t>
+          <t>N_1992</t>
         </is>
       </c>
       <c r="B1295" t="n">
@@ -58718,7 +58718,7 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>N_2000</t>
+          <t>N_1993</t>
         </is>
       </c>
       <c r="B1296" t="n">
@@ -58763,7 +58763,7 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>N_2001</t>
+          <t>N_1994</t>
         </is>
       </c>
       <c r="B1297" t="n">
@@ -58808,7 +58808,7 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>N_2002</t>
+          <t>N_1995</t>
         </is>
       </c>
       <c r="B1298" t="n">
@@ -58853,7 +58853,7 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>N_2004</t>
+          <t>N_1997</t>
         </is>
       </c>
       <c r="B1299" t="n">
@@ -58898,7 +58898,7 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>N_2007</t>
+          <t>N_2000</t>
         </is>
       </c>
       <c r="B1300" t="n">
@@ -58943,7 +58943,7 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>N_2008</t>
+          <t>N_2001</t>
         </is>
       </c>
       <c r="B1301" t="n">
@@ -58988,7 +58988,7 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>N_2009</t>
+          <t>N_2002</t>
         </is>
       </c>
       <c r="B1302" t="n">
@@ -59033,7 +59033,7 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>N_2010</t>
+          <t>N_2003</t>
         </is>
       </c>
       <c r="B1303" t="n">
@@ -59078,7 +59078,7 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>N_2011</t>
+          <t>N_2004</t>
         </is>
       </c>
       <c r="B1304" t="n">
@@ -59123,7 +59123,7 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>N_2013</t>
+          <t>N_2006</t>
         </is>
       </c>
       <c r="B1305" t="n">
@@ -59168,7 +59168,7 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>N_2015</t>
+          <t>N_2008</t>
         </is>
       </c>
       <c r="B1306" t="n">
@@ -59213,7 +59213,7 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>N_2017</t>
+          <t>N_2010</t>
         </is>
       </c>
       <c r="B1307" t="n">
@@ -59258,7 +59258,7 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>N_2018</t>
+          <t>N_2011</t>
         </is>
       </c>
       <c r="B1308" t="n">
@@ -59303,7 +59303,7 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>N_2020</t>
+          <t>N_2013</t>
         </is>
       </c>
       <c r="B1309" t="n">
@@ -59348,7 +59348,7 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>N_2021</t>
+          <t>N_2014</t>
         </is>
       </c>
       <c r="B1310" t="n">
@@ -59393,7 +59393,7 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>N_2022</t>
+          <t>N_2015</t>
         </is>
       </c>
       <c r="B1311" t="n">
@@ -59438,7 +59438,7 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>N_2025</t>
+          <t>N_2018</t>
         </is>
       </c>
       <c r="B1312" t="n">
@@ -59483,7 +59483,7 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>N_2026</t>
+          <t>N_2019</t>
         </is>
       </c>
       <c r="B1313" t="n">
@@ -59528,7 +59528,7 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>N_2028</t>
+          <t>N_2021</t>
         </is>
       </c>
       <c r="B1314" t="n">
@@ -59573,7 +59573,7 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>N_2029</t>
+          <t>N_2022</t>
         </is>
       </c>
       <c r="B1315" t="n">
@@ -59618,7 +59618,7 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>N_2030</t>
+          <t>N_2023</t>
         </is>
       </c>
       <c r="B1316" t="n">
@@ -59663,7 +59663,7 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>N_2031</t>
+          <t>N_2024</t>
         </is>
       </c>
       <c r="B1317" t="n">
@@ -59708,7 +59708,7 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>N_2032</t>
+          <t>N_2025</t>
         </is>
       </c>
       <c r="B1318" t="n">
@@ -59753,7 +59753,7 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>N_2033</t>
+          <t>N_2026</t>
         </is>
       </c>
       <c r="B1319" t="n">
@@ -59798,7 +59798,7 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>N_2034</t>
+          <t>N_2027</t>
         </is>
       </c>
       <c r="B1320" t="n">
@@ -59843,7 +59843,7 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>N_2035</t>
+          <t>N_2028</t>
         </is>
       </c>
       <c r="B1321" t="n">
@@ -59888,7 +59888,7 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>N_2036</t>
+          <t>N_2029</t>
         </is>
       </c>
       <c r="B1322" t="n">
@@ -59933,7 +59933,7 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>N_2038</t>
+          <t>N_2031</t>
         </is>
       </c>
       <c r="B1323" t="n">
@@ -59978,7 +59978,7 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>N_2040</t>
+          <t>N_2033</t>
         </is>
       </c>
       <c r="B1324" t="n">
@@ -60023,7 +60023,7 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>N_2041</t>
+          <t>N_2034</t>
         </is>
       </c>
       <c r="B1325" t="n">
@@ -60068,7 +60068,7 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>N_2043</t>
+          <t>N_2036</t>
         </is>
       </c>
       <c r="B1326" t="n">
@@ -60113,7 +60113,7 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>N_2044</t>
+          <t>N_2037</t>
         </is>
       </c>
       <c r="B1327" t="n">
@@ -60158,7 +60158,7 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>N_2045</t>
+          <t>N_2038</t>
         </is>
       </c>
       <c r="B1328" t="n">
@@ -60203,7 +60203,7 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>N_2049</t>
+          <t>N_2042</t>
         </is>
       </c>
       <c r="B1329" t="n">
@@ -60248,7 +60248,7 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>N_2058</t>
+          <t>N_2051</t>
         </is>
       </c>
       <c r="B1330" t="n">
@@ -60293,7 +60293,7 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>N_2059</t>
+          <t>N_2052</t>
         </is>
       </c>
       <c r="B1331" t="n">
@@ -60338,7 +60338,7 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>N_2060</t>
+          <t>N_2053</t>
         </is>
       </c>
       <c r="B1332" t="n">
@@ -60383,7 +60383,7 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>N_2061</t>
+          <t>N_2054</t>
         </is>
       </c>
       <c r="B1333" t="n">
@@ -60428,7 +60428,7 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>N_2062</t>
+          <t>N_2055</t>
         </is>
       </c>
       <c r="B1334" t="n">
@@ -60473,7 +60473,7 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>N_2065</t>
+          <t>N_2058</t>
         </is>
       </c>
       <c r="B1335" t="n">
@@ -60518,7 +60518,7 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>N_2068</t>
+          <t>N_2061</t>
         </is>
       </c>
       <c r="B1336" t="n">
@@ -60563,7 +60563,7 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>N_2071</t>
+          <t>N_2064</t>
         </is>
       </c>
       <c r="B1337" t="n">
@@ -60608,7 +60608,7 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>N_2074</t>
+          <t>N_2067</t>
         </is>
       </c>
       <c r="B1338" t="n">
@@ -60653,7 +60653,7 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>N_2076</t>
+          <t>N_2069</t>
         </is>
       </c>
       <c r="B1339" t="n">
@@ -60698,7 +60698,7 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>N_2081</t>
+          <t>N_2074</t>
         </is>
       </c>
       <c r="B1340" t="n">
@@ -60743,7 +60743,7 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>N_2082</t>
+          <t>N_2075</t>
         </is>
       </c>
       <c r="B1341" t="n">
@@ -60788,7 +60788,7 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>N_2083</t>
+          <t>N_2076</t>
         </is>
       </c>
       <c r="B1342" t="n">
@@ -60833,7 +60833,7 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>N_2085</t>
+          <t>N_2078</t>
         </is>
       </c>
       <c r="B1343" t="n">
@@ -60878,7 +60878,7 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>N_2088</t>
+          <t>N_2081</t>
         </is>
       </c>
       <c r="B1344" t="n">
@@ -60923,7 +60923,7 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>N_2091</t>
+          <t>N_2084</t>
         </is>
       </c>
       <c r="B1345" t="n">
@@ -60968,7 +60968,7 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>N_2092</t>
+          <t>N_2085</t>
         </is>
       </c>
       <c r="B1346" t="n">
@@ -61013,7 +61013,7 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>N_2094</t>
+          <t>N_2087</t>
         </is>
       </c>
       <c r="B1347" t="n">
@@ -61058,7 +61058,7 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>N_2095</t>
+          <t>N_2088</t>
         </is>
       </c>
       <c r="B1348" t="n">
@@ -61103,7 +61103,7 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>N_2097</t>
+          <t>N_2090</t>
         </is>
       </c>
       <c r="B1349" t="n">
@@ -61148,7 +61148,7 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>N_2101</t>
+          <t>N_2094</t>
         </is>
       </c>
       <c r="B1350" t="n">
@@ -61193,7 +61193,7 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>N_2102</t>
+          <t>N_2095</t>
         </is>
       </c>
       <c r="B1351" t="n">
@@ -61238,7 +61238,7 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>N_2103</t>
+          <t>N_2096</t>
         </is>
       </c>
       <c r="B1352" t="n">
@@ -61283,7 +61283,7 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>N_2104</t>
+          <t>N_2097</t>
         </is>
       </c>
       <c r="B1353" t="n">
@@ -61328,7 +61328,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>N_2107</t>
+          <t>N_2100</t>
         </is>
       </c>
       <c r="B1354" t="n">
@@ -61373,7 +61373,7 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>N_2108</t>
+          <t>N_2101</t>
         </is>
       </c>
       <c r="B1355" t="n">
@@ -61418,7 +61418,7 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>N_2109</t>
+          <t>N_2102</t>
         </is>
       </c>
       <c r="B1356" t="n">
@@ -61463,7 +61463,7 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>N_2115</t>
+          <t>N_2108</t>
         </is>
       </c>
       <c r="B1357" t="n">
@@ -61508,7 +61508,7 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>N_2116</t>
+          <t>N_2109</t>
         </is>
       </c>
       <c r="B1358" t="n">
@@ -61553,7 +61553,7 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>N_2118</t>
+          <t>N_2111</t>
         </is>
       </c>
       <c r="B1359" t="n">
@@ -61598,7 +61598,7 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>N_2119</t>
+          <t>N_2112</t>
         </is>
       </c>
       <c r="B1360" t="n">
@@ -61643,7 +61643,7 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>N_2127</t>
+          <t>N_2120</t>
         </is>
       </c>
       <c r="B1361" t="n">
@@ -61688,7 +61688,7 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>N_2128</t>
+          <t>N_2121</t>
         </is>
       </c>
       <c r="B1362" t="n">
@@ -61733,7 +61733,7 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>N_2135</t>
+          <t>N_2128</t>
         </is>
       </c>
       <c r="B1363" t="n">
@@ -61778,7 +61778,7 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>N_2136</t>
+          <t>N_2129</t>
         </is>
       </c>
       <c r="B1364" t="n">
@@ -61823,7 +61823,7 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>N_2139</t>
+          <t>N_2132</t>
         </is>
       </c>
       <c r="B1365" t="n">
@@ -61868,7 +61868,7 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>N_2141</t>
+          <t>N_2134</t>
         </is>
       </c>
       <c r="B1366" t="n">
@@ -61913,7 +61913,7 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>N_2155</t>
+          <t>N_2148</t>
         </is>
       </c>
       <c r="B1367" t="n">
@@ -61958,7 +61958,7 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>N_2157</t>
+          <t>N_2150</t>
         </is>
       </c>
       <c r="B1368" t="n">
@@ -62003,7 +62003,7 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>N_2162</t>
+          <t>N_2155</t>
         </is>
       </c>
       <c r="B1369" t="n">
@@ -62048,7 +62048,7 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>N_2163</t>
+          <t>N_2156</t>
         </is>
       </c>
       <c r="B1370" t="n">
@@ -62093,7 +62093,7 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>N_2164</t>
+          <t>N_2157</t>
         </is>
       </c>
       <c r="B1371" t="n">
@@ -62138,7 +62138,7 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>N_2168</t>
+          <t>N_2161</t>
         </is>
       </c>
       <c r="B1372" t="n">
@@ -62183,7 +62183,7 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>N_2170</t>
+          <t>N_2163</t>
         </is>
       </c>
       <c r="B1373" t="n">
@@ -62228,7 +62228,7 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>N_2181</t>
+          <t>N_2174</t>
         </is>
       </c>
       <c r="B1374" t="n">
@@ -62273,7 +62273,7 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>N_2182</t>
+          <t>N_2175</t>
         </is>
       </c>
       <c r="B1375" t="n">
@@ -62318,7 +62318,7 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>N_2187</t>
+          <t>N_2180</t>
         </is>
       </c>
       <c r="B1376" t="n">
@@ -62363,7 +62363,7 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>N_2188</t>
+          <t>N_2181</t>
         </is>
       </c>
       <c r="B1377" t="n">
@@ -62408,7 +62408,7 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>N_2189</t>
+          <t>N_2182</t>
         </is>
       </c>
       <c r="B1378" t="n">
@@ -62453,7 +62453,7 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>N_2190</t>
+          <t>N_2183</t>
         </is>
       </c>
       <c r="B1379" t="n">
@@ -62498,7 +62498,7 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>N_2195</t>
+          <t>N_2188</t>
         </is>
       </c>
       <c r="B1380" t="n">

--- a/output/Unassigned_Points_compact.xlsx
+++ b/output/Unassigned_Points_compact.xlsx
@@ -44363,7 +44363,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>N_1480</t>
+          <t>N_1481</t>
         </is>
       </c>
       <c r="B977" t="n">
@@ -44408,7 +44408,7 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>N_1483</t>
+          <t>N_1484</t>
         </is>
       </c>
       <c r="B978" t="n">
@@ -44453,7 +44453,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>N_1485</t>
+          <t>N_1486</t>
         </is>
       </c>
       <c r="B979" t="n">
@@ -44498,7 +44498,7 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>N_1486</t>
+          <t>N_1487</t>
         </is>
       </c>
       <c r="B980" t="n">
@@ -44543,7 +44543,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>N_1489</t>
+          <t>N_1490</t>
         </is>
       </c>
       <c r="B981" t="n">
@@ -44588,7 +44588,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>N_1490</t>
+          <t>N_1491</t>
         </is>
       </c>
       <c r="B982" t="n">
@@ -44633,7 +44633,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>N_1494</t>
+          <t>N_1497</t>
         </is>
       </c>
       <c r="B983" t="n">
@@ -44678,7 +44678,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>N_1499</t>
+          <t>N_1503</t>
         </is>
       </c>
       <c r="B984" t="n">
@@ -44723,7 +44723,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>N_1500</t>
+          <t>N_1504</t>
         </is>
       </c>
       <c r="B985" t="n">
@@ -44768,7 +44768,7 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>N_1501</t>
+          <t>N_1505</t>
         </is>
       </c>
       <c r="B986" t="n">
@@ -44813,7 +44813,7 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>N_1502</t>
+          <t>N_1506</t>
         </is>
       </c>
       <c r="B987" t="n">
@@ -44858,7 +44858,7 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>N_1503</t>
+          <t>N_1508</t>
         </is>
       </c>
       <c r="B988" t="n">
@@ -44903,7 +44903,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>N_1504</t>
+          <t>N_1509</t>
         </is>
       </c>
       <c r="B989" t="n">
@@ -44948,7 +44948,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>N_1505</t>
+          <t>N_1510</t>
         </is>
       </c>
       <c r="B990" t="n">
@@ -44993,7 +44993,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>N_1506</t>
+          <t>N_1511</t>
         </is>
       </c>
       <c r="B991" t="n">
@@ -45038,7 +45038,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>N_1507</t>
+          <t>N_1512</t>
         </is>
       </c>
       <c r="B992" t="n">
@@ -45083,7 +45083,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>N_1509</t>
+          <t>N_1514</t>
         </is>
       </c>
       <c r="B993" t="n">
@@ -45128,7 +45128,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>N_1511</t>
+          <t>N_1516</t>
         </is>
       </c>
       <c r="B994" t="n">
@@ -45173,7 +45173,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>N_1512</t>
+          <t>N_1517</t>
         </is>
       </c>
       <c r="B995" t="n">
@@ -45218,7 +45218,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>N_1514</t>
+          <t>N_1519</t>
         </is>
       </c>
       <c r="B996" t="n">
@@ -45263,7 +45263,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>N_1516</t>
+          <t>N_1522</t>
         </is>
       </c>
       <c r="B997" t="n">
@@ -45308,7 +45308,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>N_1517</t>
+          <t>N_1523</t>
         </is>
       </c>
       <c r="B998" t="n">
@@ -45353,7 +45353,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>N_1518</t>
+          <t>N_1524</t>
         </is>
       </c>
       <c r="B999" t="n">
@@ -45398,7 +45398,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>N_1523</t>
+          <t>N_1530</t>
         </is>
       </c>
       <c r="B1000" t="n">
@@ -45443,7 +45443,7 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>N_1524</t>
+          <t>N_1531</t>
         </is>
       </c>
       <c r="B1001" t="n">
@@ -45488,7 +45488,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>N_1526</t>
+          <t>N_1533</t>
         </is>
       </c>
       <c r="B1002" t="n">
@@ -45533,7 +45533,7 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>N_1527</t>
+          <t>N_1534</t>
         </is>
       </c>
       <c r="B1003" t="n">
@@ -45578,7 +45578,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>N_1530</t>
+          <t>N_1537</t>
         </is>
       </c>
       <c r="B1004" t="n">
@@ -45623,7 +45623,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>N_1531</t>
+          <t>N_1538</t>
         </is>
       </c>
       <c r="B1005" t="n">
@@ -45668,7 +45668,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>N_1533</t>
+          <t>N_1540</t>
         </is>
       </c>
       <c r="B1006" t="n">
@@ -45713,7 +45713,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>N_1536</t>
+          <t>N_1543</t>
         </is>
       </c>
       <c r="B1007" t="n">
@@ -45758,7 +45758,7 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>N_1537</t>
+          <t>N_1544</t>
         </is>
       </c>
       <c r="B1008" t="n">
@@ -45803,7 +45803,7 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>N_1538</t>
+          <t>N_1545</t>
         </is>
       </c>
       <c r="B1009" t="n">
@@ -45848,7 +45848,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>N_1539</t>
+          <t>N_1546</t>
         </is>
       </c>
       <c r="B1010" t="n">
@@ -45893,7 +45893,7 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>N_1541</t>
+          <t>N_1548</t>
         </is>
       </c>
       <c r="B1011" t="n">
@@ -45938,7 +45938,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>N_1542</t>
+          <t>N_1549</t>
         </is>
       </c>
       <c r="B1012" t="n">
@@ -45983,7 +45983,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>N_1543</t>
+          <t>N_1550</t>
         </is>
       </c>
       <c r="B1013" t="n">
@@ -46028,7 +46028,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>N_1545</t>
+          <t>N_1552</t>
         </is>
       </c>
       <c r="B1014" t="n">
@@ -46073,7 +46073,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>N_1546</t>
+          <t>N_1553</t>
         </is>
       </c>
       <c r="B1015" t="n">
@@ -46118,7 +46118,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>N_1547</t>
+          <t>N_1554</t>
         </is>
       </c>
       <c r="B1016" t="n">
@@ -46163,7 +46163,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>N_1548</t>
+          <t>N_1555</t>
         </is>
       </c>
       <c r="B1017" t="n">
@@ -46208,7 +46208,7 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>N_1549</t>
+          <t>N_1556</t>
         </is>
       </c>
       <c r="B1018" t="n">
@@ -46253,7 +46253,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>N_1550</t>
+          <t>N_1557</t>
         </is>
       </c>
       <c r="B1019" t="n">
@@ -46298,7 +46298,7 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>N_1551</t>
+          <t>N_1558</t>
         </is>
       </c>
       <c r="B1020" t="n">
@@ -46343,7 +46343,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>N_1552</t>
+          <t>N_1559</t>
         </is>
       </c>
       <c r="B1021" t="n">
@@ -46388,7 +46388,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>N_1554</t>
+          <t>N_1561</t>
         </is>
       </c>
       <c r="B1022" t="n">
@@ -46433,7 +46433,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>N_1555</t>
+          <t>N_1562</t>
         </is>
       </c>
       <c r="B1023" t="n">
@@ -46478,7 +46478,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>N_1556</t>
+          <t>N_1563</t>
         </is>
       </c>
       <c r="B1024" t="n">
@@ -46523,7 +46523,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>N_1557</t>
+          <t>N_1564</t>
         </is>
       </c>
       <c r="B1025" t="n">
@@ -46568,7 +46568,7 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>N_1558</t>
+          <t>N_1565</t>
         </is>
       </c>
       <c r="B1026" t="n">
@@ -46613,7 +46613,7 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>N_1560</t>
+          <t>N_1567</t>
         </is>
       </c>
       <c r="B1027" t="n">
@@ -46658,7 +46658,7 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>N_1563</t>
+          <t>N_1570</t>
         </is>
       </c>
       <c r="B1028" t="n">
@@ -46703,7 +46703,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>N_1565</t>
+          <t>N_1572</t>
         </is>
       </c>
       <c r="B1029" t="n">
@@ -46748,7 +46748,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>N_1566</t>
+          <t>N_1573</t>
         </is>
       </c>
       <c r="B1030" t="n">
@@ -46793,7 +46793,7 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>N_1568</t>
+          <t>N_1575</t>
         </is>
       </c>
       <c r="B1031" t="n">
@@ -46838,7 +46838,7 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>N_1569</t>
+          <t>N_1576</t>
         </is>
       </c>
       <c r="B1032" t="n">
@@ -46883,7 +46883,7 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>N_1570</t>
+          <t>N_1577</t>
         </is>
       </c>
       <c r="B1033" t="n">
@@ -46928,7 +46928,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>N_1571</t>
+          <t>N_1578</t>
         </is>
       </c>
       <c r="B1034" t="n">
@@ -46973,7 +46973,7 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>N_1572</t>
+          <t>N_1579</t>
         </is>
       </c>
       <c r="B1035" t="n">
@@ -47018,7 +47018,7 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>N_1573</t>
+          <t>N_1580</t>
         </is>
       </c>
       <c r="B1036" t="n">
@@ -47063,7 +47063,7 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>N_1574</t>
+          <t>N_1581</t>
         </is>
       </c>
       <c r="B1037" t="n">
@@ -47108,7 +47108,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>N_1575</t>
+          <t>N_1582</t>
         </is>
       </c>
       <c r="B1038" t="n">
@@ -47153,7 +47153,7 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>N_1576</t>
+          <t>N_1583</t>
         </is>
       </c>
       <c r="B1039" t="n">
@@ -47198,7 +47198,7 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>N_1577</t>
+          <t>N_1584</t>
         </is>
       </c>
       <c r="B1040" t="n">
@@ -47243,7 +47243,7 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>N_1578</t>
+          <t>N_1585</t>
         </is>
       </c>
       <c r="B1041" t="n">
@@ -47288,7 +47288,7 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>N_1579</t>
+          <t>N_1586</t>
         </is>
       </c>
       <c r="B1042" t="n">
@@ -47333,7 +47333,7 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>N_1580</t>
+          <t>N_1587</t>
         </is>
       </c>
       <c r="B1043" t="n">
@@ -47378,7 +47378,7 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>N_1581</t>
+          <t>N_1588</t>
         </is>
       </c>
       <c r="B1044" t="n">
@@ -47423,7 +47423,7 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>N_1582</t>
+          <t>N_1589</t>
         </is>
       </c>
       <c r="B1045" t="n">
@@ -47468,7 +47468,7 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>N_1583</t>
+          <t>N_1590</t>
         </is>
       </c>
       <c r="B1046" t="n">
@@ -47513,7 +47513,7 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>N_1584</t>
+          <t>N_1591</t>
         </is>
       </c>
       <c r="B1047" t="n">
@@ -47558,7 +47558,7 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>N_1586</t>
+          <t>N_1593</t>
         </is>
       </c>
       <c r="B1048" t="n">
@@ -47603,7 +47603,7 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>N_1587</t>
+          <t>N_1594</t>
         </is>
       </c>
       <c r="B1049" t="n">
@@ -47648,7 +47648,7 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>N_1589</t>
+          <t>N_1596</t>
         </is>
       </c>
       <c r="B1050" t="n">
@@ -47693,7 +47693,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>N_1590</t>
+          <t>N_1597</t>
         </is>
       </c>
       <c r="B1051" t="n">
@@ -47738,7 +47738,7 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>N_1592</t>
+          <t>N_1599</t>
         </is>
       </c>
       <c r="B1052" t="n">
@@ -47783,7 +47783,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>N_1593</t>
+          <t>N_1600</t>
         </is>
       </c>
       <c r="B1053" t="n">
@@ -47828,7 +47828,7 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>N_1598</t>
+          <t>N_1605</t>
         </is>
       </c>
       <c r="B1054" t="n">
@@ -47873,7 +47873,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>N_1599</t>
+          <t>N_1606</t>
         </is>
       </c>
       <c r="B1055" t="n">
@@ -47918,7 +47918,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>N_1600</t>
+          <t>N_1607</t>
         </is>
       </c>
       <c r="B1056" t="n">
@@ -47963,7 +47963,7 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>N_1601</t>
+          <t>N_1608</t>
         </is>
       </c>
       <c r="B1057" t="n">
@@ -48008,7 +48008,7 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>N_1602</t>
+          <t>N_1609</t>
         </is>
       </c>
       <c r="B1058" t="n">
@@ -48053,7 +48053,7 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>N_1604</t>
+          <t>N_1611</t>
         </is>
       </c>
       <c r="B1059" t="n">
@@ -48098,7 +48098,7 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>N_1605</t>
+          <t>N_1612</t>
         </is>
       </c>
       <c r="B1060" t="n">
@@ -48143,7 +48143,7 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>N_1607</t>
+          <t>N_1614</t>
         </is>
       </c>
       <c r="B1061" t="n">
@@ -48188,7 +48188,7 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>N_1608</t>
+          <t>N_1615</t>
         </is>
       </c>
       <c r="B1062" t="n">
@@ -48233,7 +48233,7 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>N_1609</t>
+          <t>N_1616</t>
         </is>
       </c>
       <c r="B1063" t="n">
@@ -48278,7 +48278,7 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>N_1610</t>
+          <t>N_1617</t>
         </is>
       </c>
       <c r="B1064" t="n">
@@ -48323,7 +48323,7 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>N_1611</t>
+          <t>N_1618</t>
         </is>
       </c>
       <c r="B1065" t="n">
@@ -48368,7 +48368,7 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>N_1612</t>
+          <t>N_1619</t>
         </is>
       </c>
       <c r="B1066" t="n">
@@ -48413,7 +48413,7 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>N_1613</t>
+          <t>N_1620</t>
         </is>
       </c>
       <c r="B1067" t="n">
@@ -48458,7 +48458,7 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>N_1614</t>
+          <t>N_1621</t>
         </is>
       </c>
       <c r="B1068" t="n">
@@ -48503,7 +48503,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>N_1615</t>
+          <t>N_1622</t>
         </is>
       </c>
       <c r="B1069" t="n">
@@ -48548,7 +48548,7 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>N_1616</t>
+          <t>N_1623</t>
         </is>
       </c>
       <c r="B1070" t="n">
@@ -48593,7 +48593,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>N_1618</t>
+          <t>N_1625</t>
         </is>
       </c>
       <c r="B1071" t="n">
@@ -48638,7 +48638,7 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>N_1620</t>
+          <t>N_1627</t>
         </is>
       </c>
       <c r="B1072" t="n">
@@ -48683,7 +48683,7 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>N_1621</t>
+          <t>N_1628</t>
         </is>
       </c>
       <c r="B1073" t="n">
@@ -48728,7 +48728,7 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>N_1623</t>
+          <t>N_1630</t>
         </is>
       </c>
       <c r="B1074" t="n">
@@ -48773,7 +48773,7 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>N_1624</t>
+          <t>N_1631</t>
         </is>
       </c>
       <c r="B1075" t="n">
@@ -48818,7 +48818,7 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>N_1625</t>
+          <t>N_1632</t>
         </is>
       </c>
       <c r="B1076" t="n">
@@ -48863,7 +48863,7 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>N_1626</t>
+          <t>N_1633</t>
         </is>
       </c>
       <c r="B1077" t="n">
@@ -48908,7 +48908,7 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>N_1627</t>
+          <t>N_1634</t>
         </is>
       </c>
       <c r="B1078" t="n">
@@ -48953,7 +48953,7 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>N_1629</t>
+          <t>N_1636</t>
         </is>
       </c>
       <c r="B1079" t="n">
@@ -48998,7 +48998,7 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>N_1631</t>
+          <t>N_1638</t>
         </is>
       </c>
       <c r="B1080" t="n">
@@ -49043,7 +49043,7 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>N_1632</t>
+          <t>N_1639</t>
         </is>
       </c>
       <c r="B1081" t="n">
@@ -49088,7 +49088,7 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>N_1633</t>
+          <t>N_1640</t>
         </is>
       </c>
       <c r="B1082" t="n">
@@ -49133,7 +49133,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>N_1634</t>
+          <t>N_1641</t>
         </is>
       </c>
       <c r="B1083" t="n">
@@ -49178,7 +49178,7 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>N_1635</t>
+          <t>N_1642</t>
         </is>
       </c>
       <c r="B1084" t="n">
@@ -49223,7 +49223,7 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>N_1636</t>
+          <t>N_1643</t>
         </is>
       </c>
       <c r="B1085" t="n">
@@ -49268,7 +49268,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>N_1637</t>
+          <t>N_1644</t>
         </is>
       </c>
       <c r="B1086" t="n">
@@ -49313,7 +49313,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>N_1638</t>
+          <t>N_1645</t>
         </is>
       </c>
       <c r="B1087" t="n">
@@ -49358,7 +49358,7 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>N_1639</t>
+          <t>N_1646</t>
         </is>
       </c>
       <c r="B1088" t="n">
@@ -49403,7 +49403,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>N_1640</t>
+          <t>N_1647</t>
         </is>
       </c>
       <c r="B1089" t="n">
@@ -49448,7 +49448,7 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>N_1642</t>
+          <t>N_1649</t>
         </is>
       </c>
       <c r="B1090" t="n">
@@ -49493,7 +49493,7 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>N_1643</t>
+          <t>N_1650</t>
         </is>
       </c>
       <c r="B1091" t="n">
@@ -49538,7 +49538,7 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>N_1644</t>
+          <t>N_1651</t>
         </is>
       </c>
       <c r="B1092" t="n">
@@ -49583,7 +49583,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>N_1645</t>
+          <t>N_1652</t>
         </is>
       </c>
       <c r="B1093" t="n">
@@ -49628,7 +49628,7 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>N_1646</t>
+          <t>N_1653</t>
         </is>
       </c>
       <c r="B1094" t="n">
@@ -49673,7 +49673,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>N_1647</t>
+          <t>N_1654</t>
         </is>
       </c>
       <c r="B1095" t="n">
@@ -49718,7 +49718,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>N_1648</t>
+          <t>N_1655</t>
         </is>
       </c>
       <c r="B1096" t="n">
@@ -49763,7 +49763,7 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>N_1649</t>
+          <t>N_1656</t>
         </is>
       </c>
       <c r="B1097" t="n">
@@ -49808,7 +49808,7 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>N_1650</t>
+          <t>N_1657</t>
         </is>
       </c>
       <c r="B1098" t="n">
@@ -49853,7 +49853,7 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>N_1653</t>
+          <t>N_1660</t>
         </is>
       </c>
       <c r="B1099" t="n">
@@ -49898,7 +49898,7 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>N_1654</t>
+          <t>N_1661</t>
         </is>
       </c>
       <c r="B1100" t="n">
@@ -49943,7 +49943,7 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>N_1655</t>
+          <t>N_1662</t>
         </is>
       </c>
       <c r="B1101" t="n">
@@ -49988,7 +49988,7 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>N_1656</t>
+          <t>N_1663</t>
         </is>
       </c>
       <c r="B1102" t="n">
@@ -50033,7 +50033,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>N_1661</t>
+          <t>N_1668</t>
         </is>
       </c>
       <c r="B1103" t="n">
@@ -50078,7 +50078,7 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>N_1663</t>
+          <t>N_1670</t>
         </is>
       </c>
       <c r="B1104" t="n">
@@ -50123,7 +50123,7 @@
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>N_1664</t>
+          <t>N_1671</t>
         </is>
       </c>
       <c r="B1105" t="n">
@@ -50168,7 +50168,7 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>N_1665</t>
+          <t>N_1672</t>
         </is>
       </c>
       <c r="B1106" t="n">
@@ -50213,7 +50213,7 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>N_1666</t>
+          <t>N_1673</t>
         </is>
       </c>
       <c r="B1107" t="n">
@@ -50258,7 +50258,7 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>N_1668</t>
+          <t>N_1675</t>
         </is>
       </c>
       <c r="B1108" t="n">
@@ -50303,7 +50303,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>N_1670</t>
+          <t>N_1677</t>
         </is>
       </c>
       <c r="B1109" t="n">
@@ -50348,7 +50348,7 @@
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>N_1672</t>
+          <t>N_1679</t>
         </is>
       </c>
       <c r="B1110" t="n">
@@ -50393,7 +50393,7 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>N_1674</t>
+          <t>N_1681</t>
         </is>
       </c>
       <c r="B1111" t="n">
@@ -50438,7 +50438,7 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>N_1675</t>
+          <t>N_1682</t>
         </is>
       </c>
       <c r="B1112" t="n">
@@ -50483,7 +50483,7 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>N_1676</t>
+          <t>N_1683</t>
         </is>
       </c>
       <c r="B1113" t="n">
@@ -50528,7 +50528,7 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>N_1678</t>
+          <t>N_1685</t>
         </is>
       </c>
       <c r="B1114" t="n">
@@ -50573,7 +50573,7 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>N_1679</t>
+          <t>N_1686</t>
         </is>
       </c>
       <c r="B1115" t="n">
@@ -50618,7 +50618,7 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>N_1680</t>
+          <t>N_1687</t>
         </is>
       </c>
       <c r="B1116" t="n">
@@ -50663,7 +50663,7 @@
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>N_1681</t>
+          <t>N_1688</t>
         </is>
       </c>
       <c r="B1117" t="n">
@@ -50708,7 +50708,7 @@
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>N_1682</t>
+          <t>N_1689</t>
         </is>
       </c>
       <c r="B1118" t="n">
@@ -50753,7 +50753,7 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>N_1683</t>
+          <t>N_1690</t>
         </is>
       </c>
       <c r="B1119" t="n">
@@ -50798,7 +50798,7 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>N_1684</t>
+          <t>N_1691</t>
         </is>
       </c>
       <c r="B1120" t="n">
@@ -50843,7 +50843,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>N_1686</t>
+          <t>N_1693</t>
         </is>
       </c>
       <c r="B1121" t="n">
@@ -50888,7 +50888,7 @@
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>N_1687</t>
+          <t>N_1694</t>
         </is>
       </c>
       <c r="B1122" t="n">
@@ -50933,7 +50933,7 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>N_1691</t>
+          <t>N_1698</t>
         </is>
       </c>
       <c r="B1123" t="n">
@@ -50978,7 +50978,7 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>N_1692</t>
+          <t>N_1699</t>
         </is>
       </c>
       <c r="B1124" t="n">
@@ -51023,7 +51023,7 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>N_1694</t>
+          <t>N_1701</t>
         </is>
       </c>
       <c r="B1125" t="n">
@@ -51068,7 +51068,7 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>N_1697</t>
+          <t>N_1704</t>
         </is>
       </c>
       <c r="B1126" t="n">
@@ -51113,7 +51113,7 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>N_1698</t>
+          <t>N_1705</t>
         </is>
       </c>
       <c r="B1127" t="n">
@@ -51158,7 +51158,7 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>N_1699</t>
+          <t>N_1706</t>
         </is>
       </c>
       <c r="B1128" t="n">
@@ -51203,7 +51203,7 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>N_1700</t>
+          <t>N_1707</t>
         </is>
       </c>
       <c r="B1129" t="n">
@@ -51248,7 +51248,7 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>N_1701</t>
+          <t>N_1708</t>
         </is>
       </c>
       <c r="B1130" t="n">
@@ -51293,7 +51293,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>N_1702</t>
+          <t>N_1709</t>
         </is>
       </c>
       <c r="B1131" t="n">
@@ -51338,7 +51338,7 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>N_1705</t>
+          <t>N_1712</t>
         </is>
       </c>
       <c r="B1132" t="n">
@@ -51383,7 +51383,7 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>N_1710</t>
+          <t>N_1717</t>
         </is>
       </c>
       <c r="B1133" t="n">
@@ -51428,7 +51428,7 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>N_1711</t>
+          <t>N_1718</t>
         </is>
       </c>
       <c r="B1134" t="n">
@@ -51473,7 +51473,7 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>N_1712</t>
+          <t>N_1719</t>
         </is>
       </c>
       <c r="B1135" t="n">
@@ -51518,7 +51518,7 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>N_1714</t>
+          <t>N_1721</t>
         </is>
       </c>
       <c r="B1136" t="n">
@@ -51563,7 +51563,7 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>N_1715</t>
+          <t>N_1722</t>
         </is>
       </c>
       <c r="B1137" t="n">
@@ -51608,7 +51608,7 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>N_1716</t>
+          <t>N_1723</t>
         </is>
       </c>
       <c r="B1138" t="n">
@@ -51653,7 +51653,7 @@
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>N_1717</t>
+          <t>N_1724</t>
         </is>
       </c>
       <c r="B1139" t="n">
@@ -51698,7 +51698,7 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>N_1718</t>
+          <t>N_1725</t>
         </is>
       </c>
       <c r="B1140" t="n">
@@ -51743,7 +51743,7 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>N_1719</t>
+          <t>N_1726</t>
         </is>
       </c>
       <c r="B1141" t="n">
@@ -51788,7 +51788,7 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>N_1722</t>
+          <t>N_1729</t>
         </is>
       </c>
       <c r="B1142" t="n">
@@ -51833,7 +51833,7 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>N_1723</t>
+          <t>N_1730</t>
         </is>
       </c>
       <c r="B1143" t="n">
@@ -51878,7 +51878,7 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>N_1727</t>
+          <t>N_1734</t>
         </is>
       </c>
       <c r="B1144" t="n">
@@ -51923,7 +51923,7 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>N_1731</t>
+          <t>N_1738</t>
         </is>
       </c>
       <c r="B1145" t="n">
@@ -51968,7 +51968,7 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>N_1734</t>
+          <t>N_1741</t>
         </is>
       </c>
       <c r="B1146" t="n">
@@ -52013,7 +52013,7 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>N_1736</t>
+          <t>N_1743</t>
         </is>
       </c>
       <c r="B1147" t="n">
@@ -52058,7 +52058,7 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>N_1737</t>
+          <t>N_1744</t>
         </is>
       </c>
       <c r="B1148" t="n">
@@ -52103,7 +52103,7 @@
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>N_1740</t>
+          <t>N_1747</t>
         </is>
       </c>
       <c r="B1149" t="n">
@@ -52148,7 +52148,7 @@
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>N_1741</t>
+          <t>N_1748</t>
         </is>
       </c>
       <c r="B1150" t="n">
@@ -52193,7 +52193,7 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>N_1743</t>
+          <t>N_1750</t>
         </is>
       </c>
       <c r="B1151" t="n">
@@ -52238,7 +52238,7 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>N_1745</t>
+          <t>N_1752</t>
         </is>
       </c>
       <c r="B1152" t="n">
@@ -52283,7 +52283,7 @@
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>N_1746</t>
+          <t>N_1753</t>
         </is>
       </c>
       <c r="B1153" t="n">
@@ -52328,7 +52328,7 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>N_1747</t>
+          <t>N_1754</t>
         </is>
       </c>
       <c r="B1154" t="n">
@@ -52373,7 +52373,7 @@
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>N_1748</t>
+          <t>N_1755</t>
         </is>
       </c>
       <c r="B1155" t="n">
@@ -52418,7 +52418,7 @@
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>N_1749</t>
+          <t>N_1756</t>
         </is>
       </c>
       <c r="B1156" t="n">
@@ -52463,7 +52463,7 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>N_1750</t>
+          <t>N_1757</t>
         </is>
       </c>
       <c r="B1157" t="n">
@@ -52508,7 +52508,7 @@
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>N_1751</t>
+          <t>N_1758</t>
         </is>
       </c>
       <c r="B1158" t="n">
@@ -52553,7 +52553,7 @@
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>N_1753</t>
+          <t>N_1760</t>
         </is>
       </c>
       <c r="B1159" t="n">
@@ -52598,7 +52598,7 @@
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>N_1754</t>
+          <t>N_1761</t>
         </is>
       </c>
       <c r="B1160" t="n">
@@ -52643,7 +52643,7 @@
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>N_1755</t>
+          <t>N_1762</t>
         </is>
       </c>
       <c r="B1161" t="n">
@@ -52688,7 +52688,7 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>N_1756</t>
+          <t>N_1763</t>
         </is>
       </c>
       <c r="B1162" t="n">
@@ -52733,7 +52733,7 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>N_1758</t>
+          <t>N_1765</t>
         </is>
       </c>
       <c r="B1163" t="n">
@@ -52778,7 +52778,7 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>N_1760</t>
+          <t>N_1767</t>
         </is>
       </c>
       <c r="B1164" t="n">
@@ -52823,7 +52823,7 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>N_1761</t>
+          <t>N_1768</t>
         </is>
       </c>
       <c r="B1165" t="n">
@@ -52868,7 +52868,7 @@
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>N_1762</t>
+          <t>N_1769</t>
         </is>
       </c>
       <c r="B1166" t="n">
@@ -52913,7 +52913,7 @@
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>N_1764</t>
+          <t>N_1771</t>
         </is>
       </c>
       <c r="B1167" t="n">
@@ -52958,7 +52958,7 @@
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>N_1767</t>
+          <t>N_1774</t>
         </is>
       </c>
       <c r="B1168" t="n">
@@ -53003,7 +53003,7 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>N_1768</t>
+          <t>N_1775</t>
         </is>
       </c>
       <c r="B1169" t="n">
@@ -53048,7 +53048,7 @@
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>N_1769</t>
+          <t>N_1776</t>
         </is>
       </c>
       <c r="B1170" t="n">
@@ -53093,7 +53093,7 @@
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>N_1770</t>
+          <t>N_1777</t>
         </is>
       </c>
       <c r="B1171" t="n">
@@ -53138,7 +53138,7 @@
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>N_1771</t>
+          <t>N_1778</t>
         </is>
       </c>
       <c r="B1172" t="n">
@@ -53183,7 +53183,7 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>N_1772</t>
+          <t>N_1779</t>
         </is>
       </c>
       <c r="B1173" t="n">
@@ -53228,7 +53228,7 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>N_1773</t>
+          <t>N_1780</t>
         </is>
       </c>
       <c r="B1174" t="n">
@@ -53273,7 +53273,7 @@
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>N_1774</t>
+          <t>N_1781</t>
         </is>
       </c>
       <c r="B1175" t="n">
@@ -53318,7 +53318,7 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>N_1775</t>
+          <t>N_1782</t>
         </is>
       </c>
       <c r="B1176" t="n">
@@ -53363,7 +53363,7 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>N_1777</t>
+          <t>N_1784</t>
         </is>
       </c>
       <c r="B1177" t="n">
@@ -53408,7 +53408,7 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>N_1778</t>
+          <t>N_1785</t>
         </is>
       </c>
       <c r="B1178" t="n">
@@ -53453,7 +53453,7 @@
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>N_1779</t>
+          <t>N_1786</t>
         </is>
       </c>
       <c r="B1179" t="n">
@@ -53498,7 +53498,7 @@
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>N_1783</t>
+          <t>N_1790</t>
         </is>
       </c>
       <c r="B1180" t="n">
@@ -53543,7 +53543,7 @@
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>N_1785</t>
+          <t>N_1792</t>
         </is>
       </c>
       <c r="B1181" t="n">
@@ -53588,7 +53588,7 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>N_1789</t>
+          <t>N_1796</t>
         </is>
       </c>
       <c r="B1182" t="n">
@@ -53633,7 +53633,7 @@
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>N_1791</t>
+          <t>N_1798</t>
         </is>
       </c>
       <c r="B1183" t="n">
@@ -53678,7 +53678,7 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>N_1792</t>
+          <t>N_1799</t>
         </is>
       </c>
       <c r="B1184" t="n">
@@ -53723,7 +53723,7 @@
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>N_1793</t>
+          <t>N_1800</t>
         </is>
       </c>
       <c r="B1185" t="n">
@@ -53768,7 +53768,7 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>N_1794</t>
+          <t>N_1801</t>
         </is>
       </c>
       <c r="B1186" t="n">
@@ -53813,7 +53813,7 @@
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>N_1795</t>
+          <t>N_1802</t>
         </is>
       </c>
       <c r="B1187" t="n">
@@ -53858,7 +53858,7 @@
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>N_1796</t>
+          <t>N_1803</t>
         </is>
       </c>
       <c r="B1188" t="n">
@@ -53903,7 +53903,7 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>N_1797</t>
+          <t>N_1804</t>
         </is>
       </c>
       <c r="B1189" t="n">
@@ -53948,7 +53948,7 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>N_1801</t>
+          <t>N_1808</t>
         </is>
       </c>
       <c r="B1190" t="n">
@@ -53993,7 +53993,7 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>N_1802</t>
+          <t>N_1809</t>
         </is>
       </c>
       <c r="B1191" t="n">
@@ -54038,7 +54038,7 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>N_1803</t>
+          <t>N_1810</t>
         </is>
       </c>
       <c r="B1192" t="n">
@@ -54083,7 +54083,7 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>N_1804</t>
+          <t>N_1811</t>
         </is>
       </c>
       <c r="B1193" t="n">
@@ -54128,7 +54128,7 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>N_1805</t>
+          <t>N_1812</t>
         </is>
       </c>
       <c r="B1194" t="n">
@@ -54173,7 +54173,7 @@
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>N_1806</t>
+          <t>N_1813</t>
         </is>
       </c>
       <c r="B1195" t="n">
@@ -54218,7 +54218,7 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>N_1807</t>
+          <t>N_1814</t>
         </is>
       </c>
       <c r="B1196" t="n">
@@ -54263,7 +54263,7 @@
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>N_1809</t>
+          <t>N_1816</t>
         </is>
       </c>
       <c r="B1197" t="n">
@@ -54308,7 +54308,7 @@
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>N_1810</t>
+          <t>N_1817</t>
         </is>
       </c>
       <c r="B1198" t="n">
@@ -54353,7 +54353,7 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>N_1812</t>
+          <t>N_1819</t>
         </is>
       </c>
       <c r="B1199" t="n">
@@ -54398,7 +54398,7 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>N_1813</t>
+          <t>N_1820</t>
         </is>
       </c>
       <c r="B1200" t="n">
@@ -54443,7 +54443,7 @@
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>N_1814</t>
+          <t>N_1821</t>
         </is>
       </c>
       <c r="B1201" t="n">
@@ -54488,7 +54488,7 @@
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>N_1815</t>
+          <t>N_1822</t>
         </is>
       </c>
       <c r="B1202" t="n">
@@ -54533,7 +54533,7 @@
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>N_1819</t>
+          <t>N_1826</t>
         </is>
       </c>
       <c r="B1203" t="n">
@@ -54578,7 +54578,7 @@
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>N_1822</t>
+          <t>N_1829</t>
         </is>
       </c>
       <c r="B1204" t="n">
@@ -54623,7 +54623,7 @@
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>N_1823</t>
+          <t>N_1830</t>
         </is>
       </c>
       <c r="B1205" t="n">
@@ -54668,7 +54668,7 @@
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>N_1824</t>
+          <t>N_1831</t>
         </is>
       </c>
       <c r="B1206" t="n">
@@ -54713,7 +54713,7 @@
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>N_1826</t>
+          <t>N_1833</t>
         </is>
       </c>
       <c r="B1207" t="n">
@@ -54758,7 +54758,7 @@
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>N_1831</t>
+          <t>N_1838</t>
         </is>
       </c>
       <c r="B1208" t="n">
@@ -54803,7 +54803,7 @@
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>N_1834</t>
+          <t>N_1841</t>
         </is>
       </c>
       <c r="B1209" t="n">
@@ -54848,7 +54848,7 @@
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>N_1835</t>
+          <t>N_1842</t>
         </is>
       </c>
       <c r="B1210" t="n">
@@ -54893,7 +54893,7 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>N_1836</t>
+          <t>N_1843</t>
         </is>
       </c>
       <c r="B1211" t="n">
@@ -54938,7 +54938,7 @@
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>N_1837</t>
+          <t>N_1844</t>
         </is>
       </c>
       <c r="B1212" t="n">
@@ -54983,7 +54983,7 @@
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>N_1838</t>
+          <t>N_1845</t>
         </is>
       </c>
       <c r="B1213" t="n">
@@ -55028,7 +55028,7 @@
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>N_1839</t>
+          <t>N_1846</t>
         </is>
       </c>
       <c r="B1214" t="n">
@@ -55073,7 +55073,7 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>N_1843</t>
+          <t>N_1850</t>
         </is>
       </c>
       <c r="B1215" t="n">
@@ -55118,7 +55118,7 @@
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>N_1844</t>
+          <t>N_1851</t>
         </is>
       </c>
       <c r="B1216" t="n">
@@ -55163,7 +55163,7 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>N_1848</t>
+          <t>N_1855</t>
         </is>
       </c>
       <c r="B1217" t="n">
@@ -55208,7 +55208,7 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>N_1849</t>
+          <t>N_1856</t>
         </is>
       </c>
       <c r="B1218" t="n">
@@ -55253,7 +55253,7 @@
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>N_1850</t>
+          <t>N_1857</t>
         </is>
       </c>
       <c r="B1219" t="n">
@@ -55298,7 +55298,7 @@
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>N_1855</t>
+          <t>N_1862</t>
         </is>
       </c>
       <c r="B1220" t="n">
@@ -55343,7 +55343,7 @@
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>N_1858</t>
+          <t>N_1865</t>
         </is>
       </c>
       <c r="B1221" t="n">
@@ -55388,7 +55388,7 @@
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>N_1859</t>
+          <t>N_1866</t>
         </is>
       </c>
       <c r="B1222" t="n">
@@ -55433,7 +55433,7 @@
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>N_1862</t>
+          <t>N_1869</t>
         </is>
       </c>
       <c r="B1223" t="n">
@@ -55478,7 +55478,7 @@
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>N_1863</t>
+          <t>N_1870</t>
         </is>
       </c>
       <c r="B1224" t="n">
@@ -55523,7 +55523,7 @@
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>N_1864</t>
+          <t>N_1871</t>
         </is>
       </c>
       <c r="B1225" t="n">
@@ -55568,7 +55568,7 @@
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>N_1869</t>
+          <t>N_1876</t>
         </is>
       </c>
       <c r="B1226" t="n">
@@ -55613,7 +55613,7 @@
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>N_1870</t>
+          <t>N_1877</t>
         </is>
       </c>
       <c r="B1227" t="n">
@@ -55658,7 +55658,7 @@
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>N_1871</t>
+          <t>N_1878</t>
         </is>
       </c>
       <c r="B1228" t="n">
@@ -55703,7 +55703,7 @@
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>N_1872</t>
+          <t>N_1879</t>
         </is>
       </c>
       <c r="B1229" t="n">
@@ -55748,7 +55748,7 @@
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>N_1873</t>
+          <t>N_1880</t>
         </is>
       </c>
       <c r="B1230" t="n">
@@ -55793,7 +55793,7 @@
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>N_1875</t>
+          <t>N_1882</t>
         </is>
       </c>
       <c r="B1231" t="n">
@@ -55838,7 +55838,7 @@
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>N_1876</t>
+          <t>N_1883</t>
         </is>
       </c>
       <c r="B1232" t="n">
@@ -55883,7 +55883,7 @@
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>N_1877</t>
+          <t>N_1884</t>
         </is>
       </c>
       <c r="B1233" t="n">
@@ -55928,7 +55928,7 @@
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>N_1879</t>
+          <t>N_1886</t>
         </is>
       </c>
       <c r="B1234" t="n">
@@ -55973,7 +55973,7 @@
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>N_1881</t>
+          <t>N_1888</t>
         </is>
       </c>
       <c r="B1235" t="n">
@@ -56018,7 +56018,7 @@
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>N_1882</t>
+          <t>N_1889</t>
         </is>
       </c>
       <c r="B1236" t="n">
@@ -56063,7 +56063,7 @@
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>N_1884</t>
+          <t>N_1891</t>
         </is>
       </c>
       <c r="B1237" t="n">
@@ -56108,7 +56108,7 @@
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>N_1888</t>
+          <t>N_1895</t>
         </is>
       </c>
       <c r="B1238" t="n">
@@ -56153,7 +56153,7 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>N_1890</t>
+          <t>N_1897</t>
         </is>
       </c>
       <c r="B1239" t="n">
@@ -56198,7 +56198,7 @@
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>N_1892</t>
+          <t>N_1899</t>
         </is>
       </c>
       <c r="B1240" t="n">
@@ -56243,7 +56243,7 @@
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>N_1896</t>
+          <t>N_1903</t>
         </is>
       </c>
       <c r="B1241" t="n">
@@ -56288,7 +56288,7 @@
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>N_1897</t>
+          <t>N_1904</t>
         </is>
       </c>
       <c r="B1242" t="n">
@@ -56333,7 +56333,7 @@
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>N_1898</t>
+          <t>N_1905</t>
         </is>
       </c>
       <c r="B1243" t="n">
@@ -56378,7 +56378,7 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>N_1903</t>
+          <t>N_1910</t>
         </is>
       </c>
       <c r="B1244" t="n">
@@ -56423,7 +56423,7 @@
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>N_1904</t>
+          <t>N_1911</t>
         </is>
       </c>
       <c r="B1245" t="n">
@@ -56468,7 +56468,7 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>N_1905</t>
+          <t>N_1912</t>
         </is>
       </c>
       <c r="B1246" t="n">
@@ -56513,7 +56513,7 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>N_1906</t>
+          <t>N_1913</t>
         </is>
       </c>
       <c r="B1247" t="n">
@@ -56558,7 +56558,7 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>N_1908</t>
+          <t>N_1915</t>
         </is>
       </c>
       <c r="B1248" t="n">
@@ -56603,7 +56603,7 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>N_1909</t>
+          <t>N_1916</t>
         </is>
       </c>
       <c r="B1249" t="n">
@@ -56648,7 +56648,7 @@
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>N_1912</t>
+          <t>N_1919</t>
         </is>
       </c>
       <c r="B1250" t="n">
@@ -56693,7 +56693,7 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>N_1916</t>
+          <t>N_1923</t>
         </is>
       </c>
       <c r="B1251" t="n">
@@ -56738,7 +56738,7 @@
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>N_1917</t>
+          <t>N_1924</t>
         </is>
       </c>
       <c r="B1252" t="n">
@@ -56783,7 +56783,7 @@
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>N_1921</t>
+          <t>N_1928</t>
         </is>
       </c>
       <c r="B1253" t="n">
@@ -56828,7 +56828,7 @@
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>N_1924</t>
+          <t>N_1931</t>
         </is>
       </c>
       <c r="B1254" t="n">
@@ -56873,7 +56873,7 @@
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>N_1925</t>
+          <t>N_1932</t>
         </is>
       </c>
       <c r="B1255" t="n">
@@ -56918,7 +56918,7 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>N_1930</t>
+          <t>N_1937</t>
         </is>
       </c>
       <c r="B1256" t="n">
@@ -56963,7 +56963,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>N_1933</t>
+          <t>N_1940</t>
         </is>
       </c>
       <c r="B1257" t="n">
@@ -57008,7 +57008,7 @@
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>N_1934</t>
+          <t>N_1941</t>
         </is>
       </c>
       <c r="B1258" t="n">
@@ -57053,7 +57053,7 @@
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>N_1935</t>
+          <t>N_1942</t>
         </is>
       </c>
       <c r="B1259" t="n">
@@ -57098,7 +57098,7 @@
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>N_1937</t>
+          <t>N_1944</t>
         </is>
       </c>
       <c r="B1260" t="n">
@@ -57143,7 +57143,7 @@
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>N_1939</t>
+          <t>N_1946</t>
         </is>
       </c>
       <c r="B1261" t="n">
@@ -57188,7 +57188,7 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>N_1940</t>
+          <t>N_1947</t>
         </is>
       </c>
       <c r="B1262" t="n">
@@ -57233,7 +57233,7 @@
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>N_1942</t>
+          <t>N_1949</t>
         </is>
       </c>
       <c r="B1263" t="n">
@@ -57278,7 +57278,7 @@
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>N_1944</t>
+          <t>N_1951</t>
         </is>
       </c>
       <c r="B1264" t="n">
@@ -57323,7 +57323,7 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>N_1945</t>
+          <t>N_1952</t>
         </is>
       </c>
       <c r="B1265" t="n">
@@ -57368,7 +57368,7 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>N_1950</t>
+          <t>N_1957</t>
         </is>
       </c>
       <c r="B1266" t="n">
@@ -57413,7 +57413,7 @@
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>N_1952</t>
+          <t>N_1959</t>
         </is>
       </c>
       <c r="B1267" t="n">
@@ -57458,7 +57458,7 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>N_1956</t>
+          <t>N_1963</t>
         </is>
       </c>
       <c r="B1268" t="n">
@@ -57503,7 +57503,7 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>N_1959</t>
+          <t>N_1966</t>
         </is>
       </c>
       <c r="B1269" t="n">
@@ -57548,7 +57548,7 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>N_1960</t>
+          <t>N_1967</t>
         </is>
       </c>
       <c r="B1270" t="n">
@@ -57593,7 +57593,7 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>N_1961</t>
+          <t>N_1968</t>
         </is>
       </c>
       <c r="B1271" t="n">
@@ -57638,7 +57638,7 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>N_1962</t>
+          <t>N_1969</t>
         </is>
       </c>
       <c r="B1272" t="n">
@@ -57683,7 +57683,7 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>N_1963</t>
+          <t>N_1970</t>
         </is>
       </c>
       <c r="B1273" t="n">
@@ -57728,7 +57728,7 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>N_1964</t>
+          <t>N_1971</t>
         </is>
       </c>
       <c r="B1274" t="n">
@@ -57773,7 +57773,7 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>N_1967</t>
+          <t>N_1974</t>
         </is>
       </c>
       <c r="B1275" t="n">
@@ -57818,7 +57818,7 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>N_1968</t>
+          <t>N_1975</t>
         </is>
       </c>
       <c r="B1276" t="n">
@@ -57863,7 +57863,7 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>N_1970</t>
+          <t>N_1977</t>
         </is>
       </c>
       <c r="B1277" t="n">
@@ -57908,7 +57908,7 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>N_1971</t>
+          <t>N_1978</t>
         </is>
       </c>
       <c r="B1278" t="n">
@@ -57953,7 +57953,7 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>N_1972</t>
+          <t>N_1979</t>
         </is>
       </c>
       <c r="B1279" t="n">
@@ -57998,7 +57998,7 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>N_1973</t>
+          <t>N_1980</t>
         </is>
       </c>
       <c r="B1280" t="n">
@@ -58043,7 +58043,7 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>N_1974</t>
+          <t>N_1981</t>
         </is>
       </c>
       <c r="B1281" t="n">
@@ -58088,7 +58088,7 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>N_1978</t>
+          <t>N_1985</t>
         </is>
       </c>
       <c r="B1282" t="n">
@@ -58133,7 +58133,7 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>N_1979</t>
+          <t>N_1986</t>
         </is>
       </c>
       <c r="B1283" t="n">
@@ -58178,7 +58178,7 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>N_1980</t>
+          <t>N_1987</t>
         </is>
       </c>
       <c r="B1284" t="n">
@@ -58223,7 +58223,7 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>N_1981</t>
+          <t>N_1988</t>
         </is>
       </c>
       <c r="B1285" t="n">
@@ -58268,7 +58268,7 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>N_1982</t>
+          <t>N_1989</t>
         </is>
       </c>
       <c r="B1286" t="n">
@@ -58313,7 +58313,7 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>N_1983</t>
+          <t>N_1990</t>
         </is>
       </c>
       <c r="B1287" t="n">
@@ -58358,7 +58358,7 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>N_1984</t>
+          <t>N_1991</t>
         </is>
       </c>
       <c r="B1288" t="n">
@@ -58403,7 +58403,7 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>N_1985</t>
+          <t>N_1992</t>
         </is>
       </c>
       <c r="B1289" t="n">
@@ -58448,7 +58448,7 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>N_1986</t>
+          <t>N_1993</t>
         </is>
       </c>
       <c r="B1290" t="n">
@@ -58493,7 +58493,7 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>N_1987</t>
+          <t>N_1994</t>
         </is>
       </c>
       <c r="B1291" t="n">
@@ -58538,7 +58538,7 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>N_1988</t>
+          <t>N_1995</t>
         </is>
       </c>
       <c r="B1292" t="n">
@@ -58583,7 +58583,7 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>N_1989</t>
+          <t>N_1996</t>
         </is>
       </c>
       <c r="B1293" t="n">
@@ -58628,7 +58628,7 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>N_1991</t>
+          <t>N_1998</t>
         </is>
       </c>
       <c r="B1294" t="n">
@@ -58673,7 +58673,7 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>N_1992</t>
+          <t>N_1999</t>
         </is>
       </c>
       <c r="B1295" t="n">
@@ -58718,7 +58718,7 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>N_1993</t>
+          <t>N_2000</t>
         </is>
       </c>
       <c r="B1296" t="n">
@@ -58763,7 +58763,7 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>N_1994</t>
+          <t>N_2001</t>
         </is>
       </c>
       <c r="B1297" t="n">
@@ -58808,7 +58808,7 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>N_1995</t>
+          <t>N_2002</t>
         </is>
       </c>
       <c r="B1298" t="n">
@@ -58853,7 +58853,7 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>N_1997</t>
+          <t>N_2004</t>
         </is>
       </c>
       <c r="B1299" t="n">
@@ -58898,7 +58898,7 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>N_2000</t>
+          <t>N_2007</t>
         </is>
       </c>
       <c r="B1300" t="n">
@@ -58943,7 +58943,7 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>N_2001</t>
+          <t>N_2008</t>
         </is>
       </c>
       <c r="B1301" t="n">
@@ -58988,7 +58988,7 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>N_2002</t>
+          <t>N_2009</t>
         </is>
       </c>
       <c r="B1302" t="n">
@@ -59033,7 +59033,7 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>N_2003</t>
+          <t>N_2010</t>
         </is>
       </c>
       <c r="B1303" t="n">
@@ -59078,7 +59078,7 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>N_2004</t>
+          <t>N_2011</t>
         </is>
       </c>
       <c r="B1304" t="n">
@@ -59123,7 +59123,7 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>N_2006</t>
+          <t>N_2013</t>
         </is>
       </c>
       <c r="B1305" t="n">
@@ -59168,7 +59168,7 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>N_2008</t>
+          <t>N_2015</t>
         </is>
       </c>
       <c r="B1306" t="n">
@@ -59213,7 +59213,7 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>N_2010</t>
+          <t>N_2017</t>
         </is>
       </c>
       <c r="B1307" t="n">
@@ -59258,7 +59258,7 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>N_2011</t>
+          <t>N_2018</t>
         </is>
       </c>
       <c r="B1308" t="n">
@@ -59303,7 +59303,7 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>N_2013</t>
+          <t>N_2020</t>
         </is>
       </c>
       <c r="B1309" t="n">
@@ -59348,7 +59348,7 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>N_2014</t>
+          <t>N_2021</t>
         </is>
       </c>
       <c r="B1310" t="n">
@@ -59393,7 +59393,7 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>N_2015</t>
+          <t>N_2022</t>
         </is>
       </c>
       <c r="B1311" t="n">
@@ -59438,7 +59438,7 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>N_2018</t>
+          <t>N_2025</t>
         </is>
       </c>
       <c r="B1312" t="n">
@@ -59483,7 +59483,7 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>N_2019</t>
+          <t>N_2026</t>
         </is>
       </c>
       <c r="B1313" t="n">
@@ -59528,7 +59528,7 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>N_2021</t>
+          <t>N_2028</t>
         </is>
       </c>
       <c r="B1314" t="n">
@@ -59573,7 +59573,7 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>N_2022</t>
+          <t>N_2029</t>
         </is>
       </c>
       <c r="B1315" t="n">
@@ -59618,7 +59618,7 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>N_2023</t>
+          <t>N_2030</t>
         </is>
       </c>
       <c r="B1316" t="n">
@@ -59663,7 +59663,7 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>N_2024</t>
+          <t>N_2031</t>
         </is>
       </c>
       <c r="B1317" t="n">
@@ -59708,7 +59708,7 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>N_2025</t>
+          <t>N_2032</t>
         </is>
       </c>
       <c r="B1318" t="n">
@@ -59753,7 +59753,7 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>N_2026</t>
+          <t>N_2033</t>
         </is>
       </c>
       <c r="B1319" t="n">
@@ -59798,7 +59798,7 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>N_2027</t>
+          <t>N_2034</t>
         </is>
       </c>
       <c r="B1320" t="n">
@@ -59843,7 +59843,7 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>N_2028</t>
+          <t>N_2035</t>
         </is>
       </c>
       <c r="B1321" t="n">
@@ -59888,7 +59888,7 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>N_2029</t>
+          <t>N_2036</t>
         </is>
       </c>
       <c r="B1322" t="n">
@@ -59933,7 +59933,7 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>N_2031</t>
+          <t>N_2038</t>
         </is>
       </c>
       <c r="B1323" t="n">
@@ -59978,7 +59978,7 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>N_2033</t>
+          <t>N_2040</t>
         </is>
       </c>
       <c r="B1324" t="n">
@@ -60023,7 +60023,7 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>N_2034</t>
+          <t>N_2041</t>
         </is>
       </c>
       <c r="B1325" t="n">
@@ -60068,7 +60068,7 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>N_2036</t>
+          <t>N_2043</t>
         </is>
       </c>
       <c r="B1326" t="n">
@@ -60113,7 +60113,7 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>N_2037</t>
+          <t>N_2044</t>
         </is>
       </c>
       <c r="B1327" t="n">
@@ -60158,7 +60158,7 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>N_2038</t>
+          <t>N_2045</t>
         </is>
       </c>
       <c r="B1328" t="n">
@@ -60203,7 +60203,7 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>N_2042</t>
+          <t>N_2049</t>
         </is>
       </c>
       <c r="B1329" t="n">
@@ -60248,7 +60248,7 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>N_2051</t>
+          <t>N_2058</t>
         </is>
       </c>
       <c r="B1330" t="n">
@@ -60293,7 +60293,7 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>N_2052</t>
+          <t>N_2059</t>
         </is>
       </c>
       <c r="B1331" t="n">
@@ -60338,7 +60338,7 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>N_2053</t>
+          <t>N_2060</t>
         </is>
       </c>
       <c r="B1332" t="n">
@@ -60383,7 +60383,7 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>N_2054</t>
+          <t>N_2061</t>
         </is>
       </c>
       <c r="B1333" t="n">
@@ -60428,7 +60428,7 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>N_2055</t>
+          <t>N_2062</t>
         </is>
       </c>
       <c r="B1334" t="n">
@@ -60473,7 +60473,7 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>N_2058</t>
+          <t>N_2065</t>
         </is>
       </c>
       <c r="B1335" t="n">
@@ -60518,7 +60518,7 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>N_2061</t>
+          <t>N_2068</t>
         </is>
       </c>
       <c r="B1336" t="n">
@@ -60563,7 +60563,7 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>N_2064</t>
+          <t>N_2071</t>
         </is>
       </c>
       <c r="B1337" t="n">
@@ -60608,7 +60608,7 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>N_2067</t>
+          <t>N_2074</t>
         </is>
       </c>
       <c r="B1338" t="n">
@@ -60653,7 +60653,7 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>N_2069</t>
+          <t>N_2076</t>
         </is>
       </c>
       <c r="B1339" t="n">
@@ -60698,7 +60698,7 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>N_2074</t>
+          <t>N_2081</t>
         </is>
       </c>
       <c r="B1340" t="n">
@@ -60743,7 +60743,7 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>N_2075</t>
+          <t>N_2082</t>
         </is>
       </c>
       <c r="B1341" t="n">
@@ -60788,7 +60788,7 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>N_2076</t>
+          <t>N_2083</t>
         </is>
       </c>
       <c r="B1342" t="n">
@@ -60833,7 +60833,7 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>N_2078</t>
+          <t>N_2085</t>
         </is>
       </c>
       <c r="B1343" t="n">
@@ -60878,7 +60878,7 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>N_2081</t>
+          <t>N_2088</t>
         </is>
       </c>
       <c r="B1344" t="n">
@@ -60923,7 +60923,7 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>N_2084</t>
+          <t>N_2091</t>
         </is>
       </c>
       <c r="B1345" t="n">
@@ -60968,7 +60968,7 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>N_2085</t>
+          <t>N_2092</t>
         </is>
       </c>
       <c r="B1346" t="n">
@@ -61013,7 +61013,7 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>N_2087</t>
+          <t>N_2094</t>
         </is>
       </c>
       <c r="B1347" t="n">
@@ -61058,7 +61058,7 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>N_2088</t>
+          <t>N_2095</t>
         </is>
       </c>
       <c r="B1348" t="n">
@@ -61103,7 +61103,7 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>N_2090</t>
+          <t>N_2097</t>
         </is>
       </c>
       <c r="B1349" t="n">
@@ -61148,7 +61148,7 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>N_2094</t>
+          <t>N_2101</t>
         </is>
       </c>
       <c r="B1350" t="n">
@@ -61193,7 +61193,7 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>N_2095</t>
+          <t>N_2102</t>
         </is>
       </c>
       <c r="B1351" t="n">
@@ -61238,7 +61238,7 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>N_2096</t>
+          <t>N_2103</t>
         </is>
       </c>
       <c r="B1352" t="n">
@@ -61283,7 +61283,7 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>N_2097</t>
+          <t>N_2104</t>
         </is>
       </c>
       <c r="B1353" t="n">
@@ -61328,7 +61328,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>N_2100</t>
+          <t>N_2107</t>
         </is>
       </c>
       <c r="B1354" t="n">
@@ -61373,7 +61373,7 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>N_2101</t>
+          <t>N_2108</t>
         </is>
       </c>
       <c r="B1355" t="n">
@@ -61418,7 +61418,7 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>N_2102</t>
+          <t>N_2109</t>
         </is>
       </c>
       <c r="B1356" t="n">
@@ -61463,7 +61463,7 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>N_2108</t>
+          <t>N_2115</t>
         </is>
       </c>
       <c r="B1357" t="n">
@@ -61508,7 +61508,7 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>N_2109</t>
+          <t>N_2116</t>
         </is>
       </c>
       <c r="B1358" t="n">
@@ -61553,7 +61553,7 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>N_2111</t>
+          <t>N_2118</t>
         </is>
       </c>
       <c r="B1359" t="n">
@@ -61598,7 +61598,7 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>N_2112</t>
+          <t>N_2119</t>
         </is>
       </c>
       <c r="B1360" t="n">
@@ -61643,7 +61643,7 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>N_2120</t>
+          <t>N_2127</t>
         </is>
       </c>
       <c r="B1361" t="n">
@@ -61688,7 +61688,7 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>N_2121</t>
+          <t>N_2128</t>
         </is>
       </c>
       <c r="B1362" t="n">
@@ -61733,7 +61733,7 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>N_2128</t>
+          <t>N_2135</t>
         </is>
       </c>
       <c r="B1363" t="n">
@@ -61778,7 +61778,7 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>N_2129</t>
+          <t>N_2136</t>
         </is>
       </c>
       <c r="B1364" t="n">
@@ -61823,7 +61823,7 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>N_2132</t>
+          <t>N_2139</t>
         </is>
       </c>
       <c r="B1365" t="n">
@@ -61868,7 +61868,7 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>N_2134</t>
+          <t>N_2141</t>
         </is>
       </c>
       <c r="B1366" t="n">
@@ -61913,7 +61913,7 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>N_2148</t>
+          <t>N_2155</t>
         </is>
       </c>
       <c r="B1367" t="n">
@@ -61958,7 +61958,7 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>N_2150</t>
+          <t>N_2157</t>
         </is>
       </c>
       <c r="B1368" t="n">
@@ -62003,7 +62003,7 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>N_2155</t>
+          <t>N_2162</t>
         </is>
       </c>
       <c r="B1369" t="n">
@@ -62048,7 +62048,7 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>N_2156</t>
+          <t>N_2163</t>
         </is>
       </c>
       <c r="B1370" t="n">
@@ -62093,7 +62093,7 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>N_2157</t>
+          <t>N_2164</t>
         </is>
       </c>
       <c r="B1371" t="n">
@@ -62138,7 +62138,7 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>N_2161</t>
+          <t>N_2168</t>
         </is>
       </c>
       <c r="B1372" t="n">
@@ -62183,7 +62183,7 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>N_2163</t>
+          <t>N_2170</t>
         </is>
       </c>
       <c r="B1373" t="n">
@@ -62228,7 +62228,7 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>N_2174</t>
+          <t>N_2181</t>
         </is>
       </c>
       <c r="B1374" t="n">
@@ -62273,7 +62273,7 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>N_2175</t>
+          <t>N_2182</t>
         </is>
       </c>
       <c r="B1375" t="n">
@@ -62318,7 +62318,7 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>N_2180</t>
+          <t>N_2187</t>
         </is>
       </c>
       <c r="B1376" t="n">
@@ -62363,7 +62363,7 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>N_2181</t>
+          <t>N_2188</t>
         </is>
       </c>
       <c r="B1377" t="n">
@@ -62408,7 +62408,7 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>N_2182</t>
+          <t>N_2189</t>
         </is>
       </c>
       <c r="B1378" t="n">
@@ -62453,7 +62453,7 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>N_2183</t>
+          <t>N_2190</t>
         </is>
       </c>
       <c r="B1379" t="n">
@@ -62498,7 +62498,7 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>N_2188</t>
+          <t>N_2195</t>
         </is>
       </c>
       <c r="B1380" t="n">
